--- a/plantillas/3_Inventarios_y_Compras/04_Cuadro_Comparativo_de_Cotizaciones.xlsx
+++ b/plantillas/3_Inventarios_y_Compras/04_Cuadro_Comparativo_de_Cotizaciones.xlsx
@@ -518,7 +518,7 @@
   <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="19.25" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="E29" s="13">
-        <f>IFERROR(INDEX({"Proveedor A","Proveedor B","Proveedor C","Proveedor D"},MATCH(MIN(F25,H25,J25,L25),CHOOSE({1,2,3,4},F25,H25,J25,L25),0)),"")</f>
+        <f>IF(MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25))=1E+99,"",IF(F25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),E6,IF(H25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),G6,IF(J25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),I6,IF(L25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),K6,"")))))</f>
         <v/>
       </c>
     </row>

--- a/plantillas/3_Inventarios_y_Compras/04_Cuadro_Comparativo_de_Cotizaciones.xlsx
+++ b/plantillas/3_Inventarios_y_Compras/04_Cuadro_Comparativo_de_Cotizaciones.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.##"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,11 @@
     <font>
       <i val="1"/>
       <color rgb="00595959"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00A6A6A6"/>
+      <sz val="8"/>
     </font>
     <font>
       <b val="1"/>
@@ -92,13 +97,45 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <top style="dashed">
+        <color rgb="00A6A6A6"/>
+      </top>
+    </border>
+    <border>
+      <right style="dashed">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="dashed">
+        <color rgb="00A6A6A6"/>
+      </top>
+    </border>
+    <border>
+      <left style="dashed">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <bottom style="dashed">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="dashed">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <bottom style="dashed">
+        <color rgb="00A6A6A6"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -118,38 +155,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -532,609 +576,627 @@
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>CUADRO COMPARATIVO DE COTIZACIONES</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>INSERTE SU LOGO
+(clic derecho &gt; Insertar imagen)</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Compara hasta 4 proveedores y selecciona la mejor opción</t>
         </is>
       </c>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Requisición No.</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="4" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="9" t="n"/>
     </row>
     <row r="6">
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Proveedor A</t>
         </is>
       </c>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>Proveedor B</t>
         </is>
       </c>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>Proveedor C</t>
         </is>
       </c>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>Proveedor D</t>
         </is>
       </c>
-      <c r="L6" s="7" t="n"/>
+      <c r="L6" s="12" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Part.</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>P. Unit.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>Importe</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>P. Unit.</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>Importe</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>P. Unit.</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>Importe</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K7" s="13" t="inlineStr">
         <is>
           <t>P. Unit.</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="L7" s="13" t="inlineStr">
         <is>
           <t>Importe</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="12">
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="17">
         <f>IF(OR(E8="",$D8=""),"",E8*$D8)</f>
         <v/>
       </c>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="12">
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="17">
         <f>IF(OR(G8="",$D8=""),"",G8*$D8)</f>
         <v/>
       </c>
-      <c r="I8" s="11" t="n"/>
-      <c r="J8" s="12">
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="17">
         <f>IF(OR(I8="",$D8=""),"",I8*$D8)</f>
         <v/>
       </c>
-      <c r="K8" s="11" t="n"/>
-      <c r="L8" s="12">
+      <c r="K8" s="16" t="n"/>
+      <c r="L8" s="17">
         <f>IF(OR(K8="",$D8=""),"",K8*$D8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="12">
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="17">
         <f>IF(OR(E9="",$D9=""),"",E9*$D9)</f>
         <v/>
       </c>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="12">
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="17">
         <f>IF(OR(G9="",$D9=""),"",G9*$D9)</f>
         <v/>
       </c>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="12">
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="17">
         <f>IF(OR(I9="",$D9=""),"",I9*$D9)</f>
         <v/>
       </c>
-      <c r="K9" s="11" t="n"/>
-      <c r="L9" s="12">
+      <c r="K9" s="16" t="n"/>
+      <c r="L9" s="17">
         <f>IF(OR(K9="",$D9=""),"",K9*$D9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n">
+      <c r="A10" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="12">
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="17">
         <f>IF(OR(E10="",$D10=""),"",E10*$D10)</f>
         <v/>
       </c>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="12">
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="17">
         <f>IF(OR(G10="",$D10=""),"",G10*$D10)</f>
         <v/>
       </c>
-      <c r="I10" s="11" t="n"/>
-      <c r="J10" s="12">
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="17">
         <f>IF(OR(I10="",$D10=""),"",I10*$D10)</f>
         <v/>
       </c>
-      <c r="K10" s="11" t="n"/>
-      <c r="L10" s="12">
+      <c r="K10" s="16" t="n"/>
+      <c r="L10" s="17">
         <f>IF(OR(K10="",$D10=""),"",K10*$D10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n">
+      <c r="A11" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="12">
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="17">
         <f>IF(OR(E11="",$D11=""),"",E11*$D11)</f>
         <v/>
       </c>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="12">
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="17">
         <f>IF(OR(G11="",$D11=""),"",G11*$D11)</f>
         <v/>
       </c>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="12">
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="17">
         <f>IF(OR(I11="",$D11=""),"",I11*$D11)</f>
         <v/>
       </c>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="12">
+      <c r="K11" s="16" t="n"/>
+      <c r="L11" s="17">
         <f>IF(OR(K11="",$D11=""),"",K11*$D11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n">
+      <c r="A12" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="12">
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="17">
         <f>IF(OR(E12="",$D12=""),"",E12*$D12)</f>
         <v/>
       </c>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="12">
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="17">
         <f>IF(OR(G12="",$D12=""),"",G12*$D12)</f>
         <v/>
       </c>
-      <c r="I12" s="11" t="n"/>
-      <c r="J12" s="12">
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="17">
         <f>IF(OR(I12="",$D12=""),"",I12*$D12)</f>
         <v/>
       </c>
-      <c r="K12" s="11" t="n"/>
-      <c r="L12" s="12">
+      <c r="K12" s="16" t="n"/>
+      <c r="L12" s="17">
         <f>IF(OR(K12="",$D12=""),"",K12*$D12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n">
+      <c r="A13" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="12">
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="17">
         <f>IF(OR(E13="",$D13=""),"",E13*$D13)</f>
         <v/>
       </c>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="12">
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="17">
         <f>IF(OR(G13="",$D13=""),"",G13*$D13)</f>
         <v/>
       </c>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="12">
+      <c r="I13" s="16" t="n"/>
+      <c r="J13" s="17">
         <f>IF(OR(I13="",$D13=""),"",I13*$D13)</f>
         <v/>
       </c>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="12">
+      <c r="K13" s="16" t="n"/>
+      <c r="L13" s="17">
         <f>IF(OR(K13="",$D13=""),"",K13*$D13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n">
+      <c r="A14" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="12">
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="17">
         <f>IF(OR(E14="",$D14=""),"",E14*$D14)</f>
         <v/>
       </c>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="12">
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="17">
         <f>IF(OR(G14="",$D14=""),"",G14*$D14)</f>
         <v/>
       </c>
-      <c r="I14" s="11" t="n"/>
-      <c r="J14" s="12">
+      <c r="I14" s="16" t="n"/>
+      <c r="J14" s="17">
         <f>IF(OR(I14="",$D14=""),"",I14*$D14)</f>
         <v/>
       </c>
-      <c r="K14" s="11" t="n"/>
-      <c r="L14" s="12">
+      <c r="K14" s="16" t="n"/>
+      <c r="L14" s="17">
         <f>IF(OR(K14="",$D14=""),"",K14*$D14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n">
+      <c r="A15" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="12">
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="17">
         <f>IF(OR(E15="",$D15=""),"",E15*$D15)</f>
         <v/>
       </c>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="12">
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="17">
         <f>IF(OR(G15="",$D15=""),"",G15*$D15)</f>
         <v/>
       </c>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="12">
+      <c r="I15" s="16" t="n"/>
+      <c r="J15" s="17">
         <f>IF(OR(I15="",$D15=""),"",I15*$D15)</f>
         <v/>
       </c>
-      <c r="K15" s="11" t="n"/>
-      <c r="L15" s="12">
+      <c r="K15" s="16" t="n"/>
+      <c r="L15" s="17">
         <f>IF(OR(K15="",$D15=""),"",K15*$D15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n">
+      <c r="A16" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="12">
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="17">
         <f>IF(OR(E16="",$D16=""),"",E16*$D16)</f>
         <v/>
       </c>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="12">
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="17">
         <f>IF(OR(G16="",$D16=""),"",G16*$D16)</f>
         <v/>
       </c>
-      <c r="I16" s="11" t="n"/>
-      <c r="J16" s="12">
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="17">
         <f>IF(OR(I16="",$D16=""),"",I16*$D16)</f>
         <v/>
       </c>
-      <c r="K16" s="11" t="n"/>
-      <c r="L16" s="12">
+      <c r="K16" s="16" t="n"/>
+      <c r="L16" s="17">
         <f>IF(OR(K16="",$D16=""),"",K16*$D16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n">
+      <c r="A17" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="12">
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="17">
         <f>IF(OR(E17="",$D17=""),"",E17*$D17)</f>
         <v/>
       </c>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="12">
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="17">
         <f>IF(OR(G17="",$D17=""),"",G17*$D17)</f>
         <v/>
       </c>
-      <c r="I17" s="11" t="n"/>
-      <c r="J17" s="12">
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="17">
         <f>IF(OR(I17="",$D17=""),"",I17*$D17)</f>
         <v/>
       </c>
-      <c r="K17" s="11" t="n"/>
-      <c r="L17" s="12">
+      <c r="K17" s="16" t="n"/>
+      <c r="L17" s="17">
         <f>IF(OR(K17="",$D17=""),"",K17*$D17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n">
+      <c r="A18" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="12">
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="17">
         <f>IF(OR(E18="",$D18=""),"",E18*$D18)</f>
         <v/>
       </c>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="12">
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="17">
         <f>IF(OR(G18="",$D18=""),"",G18*$D18)</f>
         <v/>
       </c>
-      <c r="I18" s="11" t="n"/>
-      <c r="J18" s="12">
+      <c r="I18" s="16" t="n"/>
+      <c r="J18" s="17">
         <f>IF(OR(I18="",$D18=""),"",I18*$D18)</f>
         <v/>
       </c>
-      <c r="K18" s="11" t="n"/>
-      <c r="L18" s="12">
+      <c r="K18" s="16" t="n"/>
+      <c r="L18" s="17">
         <f>IF(OR(K18="",$D18=""),"",K18*$D18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n">
+      <c r="A19" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="12">
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="17">
         <f>IF(OR(E19="",$D19=""),"",E19*$D19)</f>
         <v/>
       </c>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="12">
+      <c r="G19" s="16" t="n"/>
+      <c r="H19" s="17">
         <f>IF(OR(G19="",$D19=""),"",G19*$D19)</f>
         <v/>
       </c>
-      <c r="I19" s="11" t="n"/>
-      <c r="J19" s="12">
+      <c r="I19" s="16" t="n"/>
+      <c r="J19" s="17">
         <f>IF(OR(I19="",$D19=""),"",I19*$D19)</f>
         <v/>
       </c>
-      <c r="K19" s="11" t="n"/>
-      <c r="L19" s="12">
+      <c r="K19" s="16" t="n"/>
+      <c r="L19" s="17">
         <f>IF(OR(K19="",$D19=""),"",K19*$D19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n">
+      <c r="A20" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="12">
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="17">
         <f>IF(OR(E20="",$D20=""),"",E20*$D20)</f>
         <v/>
       </c>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="12">
+      <c r="G20" s="16" t="n"/>
+      <c r="H20" s="17">
         <f>IF(OR(G20="",$D20=""),"",G20*$D20)</f>
         <v/>
       </c>
-      <c r="I20" s="11" t="n"/>
-      <c r="J20" s="12">
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="17">
         <f>IF(OR(I20="",$D20=""),"",I20*$D20)</f>
         <v/>
       </c>
-      <c r="K20" s="11" t="n"/>
-      <c r="L20" s="12">
+      <c r="K20" s="16" t="n"/>
+      <c r="L20" s="17">
         <f>IF(OR(K20="",$D20=""),"",K20*$D20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n">
+      <c r="A21" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="12">
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="17">
         <f>IF(OR(E21="",$D21=""),"",E21*$D21)</f>
         <v/>
       </c>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="12">
+      <c r="G21" s="16" t="n"/>
+      <c r="H21" s="17">
         <f>IF(OR(G21="",$D21=""),"",G21*$D21)</f>
         <v/>
       </c>
-      <c r="I21" s="11" t="n"/>
-      <c r="J21" s="12">
+      <c r="I21" s="16" t="n"/>
+      <c r="J21" s="17">
         <f>IF(OR(I21="",$D21=""),"",I21*$D21)</f>
         <v/>
       </c>
-      <c r="K21" s="11" t="n"/>
-      <c r="L21" s="12">
+      <c r="K21" s="16" t="n"/>
+      <c r="L21" s="17">
         <f>IF(OR(K21="",$D21=""),"",K21*$D21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n">
+      <c r="A22" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="12">
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="17">
         <f>IF(OR(E22="",$D22=""),"",E22*$D22)</f>
         <v/>
       </c>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="12">
+      <c r="G22" s="16" t="n"/>
+      <c r="H22" s="17">
         <f>IF(OR(G22="",$D22=""),"",G22*$D22)</f>
         <v/>
       </c>
-      <c r="I22" s="11" t="n"/>
-      <c r="J22" s="12">
+      <c r="I22" s="16" t="n"/>
+      <c r="J22" s="17">
         <f>IF(OR(I22="",$D22=""),"",I22*$D22)</f>
         <v/>
       </c>
-      <c r="K22" s="11" t="n"/>
-      <c r="L22" s="12">
+      <c r="K22" s="16" t="n"/>
+      <c r="L22" s="17">
         <f>IF(OR(K22="",$D22=""),"",K22*$D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="19">
         <f>SUM(F8:F22)</f>
         <v/>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="19">
         <f>SUM(H8:H22)</f>
         <v/>
       </c>
-      <c r="J23" s="14">
+      <c r="J23" s="19">
         <f>SUM(J8:J22)</f>
         <v/>
       </c>
-      <c r="L23" s="14">
+      <c r="L23" s="19">
         <f>SUM(L8:L22)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>IVA 16%</t>
         </is>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="19">
         <f>ROUND(F23*0.16,2)</f>
         <v/>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="19">
         <f>ROUND(H23*0.16,2)</f>
         <v/>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="19">
         <f>ROUND(J23*0.16,2)</f>
         <v/>
       </c>
-      <c r="L24" s="14">
+      <c r="L24" s="19">
         <f>ROUND(L23*0.16,2)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="19">
         <f>F23+F24</f>
         <v/>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="19">
         <f>H23+H24</f>
         <v/>
       </c>
-      <c r="J25" s="14">
+      <c r="J25" s="19">
         <f>J23+J24</f>
         <v/>
       </c>
-      <c r="L25" s="14">
+      <c r="L25" s="19">
         <f>L23+L24</f>
         <v/>
       </c>
@@ -1145,10 +1207,10 @@
           <t>Condiciones de pago</t>
         </is>
       </c>
-      <c r="F26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="H26" s="9" t="n"/>
+      <c r="J26" s="9" t="n"/>
+      <c r="L26" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -1156,37 +1218,38 @@
           <t>Tiempo de entrega (días)</t>
         </is>
       </c>
-      <c r="F27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="H27" s="9" t="n"/>
+      <c r="J27" s="9" t="n"/>
+      <c r="L27" s="9" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>MEJOR OPCIÓN (menor total)</t>
         </is>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="18">
         <f>IF(MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25))=1E+99,"",IF(F25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),E6,IF(H25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),G6,IF(J25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),I6,IF(L25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),K6,"")))))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>Nota: si un proveedor no cotiza todas las partidas, su total no es comparable.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="I6:J6"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="K1:L2"/>
     <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="K6:L6"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
@@ -1202,7 +1265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1210,61 +1273,71 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>Cuadro comparativo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>Guía de uso</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n">
+      <c r="A4" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Renombra los proveedores en la fila 6.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
+      <c r="A5" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Captura descripción, unidad y cantidad de cada partida y el precio unitario ofrecido por proveedor.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Importes, IVA y total se calculan; abajo se indica el proveedor con el menor total.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Anota condiciones de pago y tiempos de entrega, pues el precio no es el único criterio.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="20" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas amarillas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Celdas amarillas = captura · Celdas grises = cálculo automático (no modificar).</t>
         </is>

--- a/plantillas/3_Inventarios_y_Compras/04_Cuadro_Comparativo_de_Cotizaciones.xlsx
+++ b/plantillas/3_Inventarios_y_Compras/04_Cuadro_Comparativo_de_Cotizaciones.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formato" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formato" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.##"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,39 +34,82 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="18"/>
+      <sz val="20"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00595959"/>
+      <color rgb="005B6B78"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00A6A6A6"/>
       <sz val="8"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
-    </font>
-    <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="007F7F7F"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="16"/>
+      <color rgb="00C9A227"/>
+      <sz val="10"/>
     </font>
     <font>
-      <i val="1"/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="26"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="002B2B2B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="005B6B78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="008A97A3"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -78,31 +121,45 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="000B2A4A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00E6ECF1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9E5"/>
+        <fgColor rgb="00FFFCF0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00EEF2F5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00C9A227"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00C9A227"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -139,61 +196,81 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D3DB"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D3DB"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D3DB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D3DB"/>
       </bottom>
+    </border>
+    <border>
+      <top style="thick">
+        <color rgb="00C9A227"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00C9A227"/>
+      </top>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -556,6 +633,190 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>GRUPO CANVILLE</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Cuadro comparativo</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="1" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Formato administrativo editable · México</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n"/>
+      <c r="D5" s="1" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="n"/>
+      <c r="D6" s="1" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>CÓMO USARLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="B11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Renombra los proveedores en la fila 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="B12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Captura descripción, unidad y cantidad de cada partida y el precio unitario ofrecido por proveedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="B13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Importes, IVA y total se calculan; abajo se indica el proveedor con el menor total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="B14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Anota condiciones de pago y tiempos de entrega, pues el precio no es el único criterio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="B15" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>LEYENDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="9" t="inlineStr"/>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Celda de captura: escribe aquí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="11" t="inlineStr"/>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Cálculo automático: no la modifiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="12" t="inlineStr"/>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Encabezados y títulos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>GRUPO CANVILLE · Formatos administrativos · v1.0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000B2A4A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -576,627 +837,636 @@
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="44" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>CUADRO COMPARATIVO DE COTIZACIONES</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="L1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="L1" s="17" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Compara hasta 4 proveedores y selecciona la mejor opción</t>
         </is>
       </c>
-      <c r="K2" s="6" t="n"/>
-      <c r="L2" s="7" t="n"/>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="19" t="n"/>
+      <c r="I2" s="19" t="n"/>
+      <c r="J2" s="19" t="n"/>
+      <c r="K2" s="20" t="n"/>
+      <c r="L2" s="21" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Requisición No.</t>
         </is>
       </c>
       <c r="B4" s="9" t="n"/>
       <c r="C4" s="9" t="n"/>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="22" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="F4" s="10" t="n"/>
+      <c r="F4" s="23" t="n"/>
       <c r="G4" s="9" t="n"/>
     </row>
     <row r="6">
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>Proveedor A</t>
         </is>
       </c>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="F6" s="25" t="n"/>
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>Proveedor B</t>
         </is>
       </c>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="H6" s="25" t="n"/>
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t>Proveedor C</t>
         </is>
       </c>
-      <c r="J6" s="12" t="n"/>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="24" t="inlineStr">
         <is>
           <t>Proveedor D</t>
         </is>
       </c>
-      <c r="L6" s="12" t="n"/>
+      <c r="L6" s="25" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Part.</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>P. Unit.</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" s="26" t="inlineStr">
         <is>
           <t>Importe</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="26" t="inlineStr">
         <is>
           <t>P. Unit.</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="26" t="inlineStr">
         <is>
           <t>Importe</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="26" t="inlineStr">
         <is>
           <t>P. Unit.</t>
         </is>
       </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="J7" s="26" t="inlineStr">
         <is>
           <t>Importe</t>
         </is>
       </c>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="K7" s="26" t="inlineStr">
         <is>
           <t>P. Unit.</t>
         </is>
       </c>
-      <c r="L7" s="13" t="inlineStr">
+      <c r="L7" s="26" t="inlineStr">
         <is>
           <t>Importe</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="11" t="n">
         <v>1</v>
       </c>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="9" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="17">
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="29">
         <f>IF(OR(E8="",$D8=""),"",E8*$D8)</f>
         <v/>
       </c>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="17">
+      <c r="G8" s="28" t="n"/>
+      <c r="H8" s="29">
         <f>IF(OR(G8="",$D8=""),"",G8*$D8)</f>
         <v/>
       </c>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="17">
+      <c r="I8" s="28" t="n"/>
+      <c r="J8" s="29">
         <f>IF(OR(I8="",$D8=""),"",I8*$D8)</f>
         <v/>
       </c>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="17">
+      <c r="K8" s="28" t="n"/>
+      <c r="L8" s="29">
         <f>IF(OR(K8="",$D8=""),"",K8*$D8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="11" t="n">
         <v>2</v>
       </c>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="9" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="17">
+      <c r="D9" s="27" t="n"/>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="29">
         <f>IF(OR(E9="",$D9=""),"",E9*$D9)</f>
         <v/>
       </c>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="17">
+      <c r="G9" s="28" t="n"/>
+      <c r="H9" s="29">
         <f>IF(OR(G9="",$D9=""),"",G9*$D9)</f>
         <v/>
       </c>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="17">
+      <c r="I9" s="28" t="n"/>
+      <c r="J9" s="29">
         <f>IF(OR(I9="",$D9=""),"",I9*$D9)</f>
         <v/>
       </c>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="17">
+      <c r="K9" s="28" t="n"/>
+      <c r="L9" s="29">
         <f>IF(OR(K9="",$D9=""),"",K9*$D9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="n">
+      <c r="A10" s="11" t="n">
         <v>3</v>
       </c>
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="9" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="17">
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="28" t="n"/>
+      <c r="F10" s="29">
         <f>IF(OR(E10="",$D10=""),"",E10*$D10)</f>
         <v/>
       </c>
-      <c r="G10" s="16" t="n"/>
-      <c r="H10" s="17">
+      <c r="G10" s="28" t="n"/>
+      <c r="H10" s="29">
         <f>IF(OR(G10="",$D10=""),"",G10*$D10)</f>
         <v/>
       </c>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="17">
+      <c r="I10" s="28" t="n"/>
+      <c r="J10" s="29">
         <f>IF(OR(I10="",$D10=""),"",I10*$D10)</f>
         <v/>
       </c>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="17">
+      <c r="K10" s="28" t="n"/>
+      <c r="L10" s="29">
         <f>IF(OR(K10="",$D10=""),"",K10*$D10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n">
+      <c r="A11" s="11" t="n">
         <v>4</v>
       </c>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="9" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="17">
+      <c r="D11" s="27" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="29">
         <f>IF(OR(E11="",$D11=""),"",E11*$D11)</f>
         <v/>
       </c>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="17">
+      <c r="G11" s="28" t="n"/>
+      <c r="H11" s="29">
         <f>IF(OR(G11="",$D11=""),"",G11*$D11)</f>
         <v/>
       </c>
-      <c r="I11" s="16" t="n"/>
-      <c r="J11" s="17">
+      <c r="I11" s="28" t="n"/>
+      <c r="J11" s="29">
         <f>IF(OR(I11="",$D11=""),"",I11*$D11)</f>
         <v/>
       </c>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="17">
+      <c r="K11" s="28" t="n"/>
+      <c r="L11" s="29">
         <f>IF(OR(K11="",$D11=""),"",K11*$D11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="11" t="n">
         <v>5</v>
       </c>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="9" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="17">
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="29">
         <f>IF(OR(E12="",$D12=""),"",E12*$D12)</f>
         <v/>
       </c>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="17">
+      <c r="G12" s="28" t="n"/>
+      <c r="H12" s="29">
         <f>IF(OR(G12="",$D12=""),"",G12*$D12)</f>
         <v/>
       </c>
-      <c r="I12" s="16" t="n"/>
-      <c r="J12" s="17">
+      <c r="I12" s="28" t="n"/>
+      <c r="J12" s="29">
         <f>IF(OR(I12="",$D12=""),"",I12*$D12)</f>
         <v/>
       </c>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="17">
+      <c r="K12" s="28" t="n"/>
+      <c r="L12" s="29">
         <f>IF(OR(K12="",$D12=""),"",K12*$D12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="11" t="n">
         <v>6</v>
       </c>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="9" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="17">
+      <c r="D13" s="27" t="n"/>
+      <c r="E13" s="28" t="n"/>
+      <c r="F13" s="29">
         <f>IF(OR(E13="",$D13=""),"",E13*$D13)</f>
         <v/>
       </c>
-      <c r="G13" s="16" t="n"/>
-      <c r="H13" s="17">
+      <c r="G13" s="28" t="n"/>
+      <c r="H13" s="29">
         <f>IF(OR(G13="",$D13=""),"",G13*$D13)</f>
         <v/>
       </c>
-      <c r="I13" s="16" t="n"/>
-      <c r="J13" s="17">
+      <c r="I13" s="28" t="n"/>
+      <c r="J13" s="29">
         <f>IF(OR(I13="",$D13=""),"",I13*$D13)</f>
         <v/>
       </c>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="17">
+      <c r="K13" s="28" t="n"/>
+      <c r="L13" s="29">
         <f>IF(OR(K13="",$D13=""),"",K13*$D13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n">
+      <c r="A14" s="11" t="n">
         <v>7</v>
       </c>
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="9" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="17">
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="29">
         <f>IF(OR(E14="",$D14=""),"",E14*$D14)</f>
         <v/>
       </c>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="17">
+      <c r="G14" s="28" t="n"/>
+      <c r="H14" s="29">
         <f>IF(OR(G14="",$D14=""),"",G14*$D14)</f>
         <v/>
       </c>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="17">
+      <c r="I14" s="28" t="n"/>
+      <c r="J14" s="29">
         <f>IF(OR(I14="",$D14=""),"",I14*$D14)</f>
         <v/>
       </c>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="17">
+      <c r="K14" s="28" t="n"/>
+      <c r="L14" s="29">
         <f>IF(OR(K14="",$D14=""),"",K14*$D14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="n">
+      <c r="A15" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="9" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="17">
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="29">
         <f>IF(OR(E15="",$D15=""),"",E15*$D15)</f>
         <v/>
       </c>
-      <c r="G15" s="16" t="n"/>
-      <c r="H15" s="17">
+      <c r="G15" s="28" t="n"/>
+      <c r="H15" s="29">
         <f>IF(OR(G15="",$D15=""),"",G15*$D15)</f>
         <v/>
       </c>
-      <c r="I15" s="16" t="n"/>
-      <c r="J15" s="17">
+      <c r="I15" s="28" t="n"/>
+      <c r="J15" s="29">
         <f>IF(OR(I15="",$D15=""),"",I15*$D15)</f>
         <v/>
       </c>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="17">
+      <c r="K15" s="28" t="n"/>
+      <c r="L15" s="29">
         <f>IF(OR(K15="",$D15=""),"",K15*$D15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="11" t="n">
         <v>9</v>
       </c>
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="9" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="17">
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="28" t="n"/>
+      <c r="F16" s="29">
         <f>IF(OR(E16="",$D16=""),"",E16*$D16)</f>
         <v/>
       </c>
-      <c r="G16" s="16" t="n"/>
-      <c r="H16" s="17">
+      <c r="G16" s="28" t="n"/>
+      <c r="H16" s="29">
         <f>IF(OR(G16="",$D16=""),"",G16*$D16)</f>
         <v/>
       </c>
-      <c r="I16" s="16" t="n"/>
-      <c r="J16" s="17">
+      <c r="I16" s="28" t="n"/>
+      <c r="J16" s="29">
         <f>IF(OR(I16="",$D16=""),"",I16*$D16)</f>
         <v/>
       </c>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="17">
+      <c r="K16" s="28" t="n"/>
+      <c r="L16" s="29">
         <f>IF(OR(K16="",$D16=""),"",K16*$D16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="11" t="n">
         <v>10</v>
       </c>
       <c r="B17" s="9" t="n"/>
       <c r="C17" s="9" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="17">
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="29">
         <f>IF(OR(E17="",$D17=""),"",E17*$D17)</f>
         <v/>
       </c>
-      <c r="G17" s="16" t="n"/>
-      <c r="H17" s="17">
+      <c r="G17" s="28" t="n"/>
+      <c r="H17" s="29">
         <f>IF(OR(G17="",$D17=""),"",G17*$D17)</f>
         <v/>
       </c>
-      <c r="I17" s="16" t="n"/>
-      <c r="J17" s="17">
+      <c r="I17" s="28" t="n"/>
+      <c r="J17" s="29">
         <f>IF(OR(I17="",$D17=""),"",I17*$D17)</f>
         <v/>
       </c>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="17">
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="29">
         <f>IF(OR(K17="",$D17=""),"",K17*$D17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="11" t="n">
         <v>11</v>
       </c>
       <c r="B18" s="9" t="n"/>
       <c r="C18" s="9" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="17">
+      <c r="D18" s="27" t="n"/>
+      <c r="E18" s="28" t="n"/>
+      <c r="F18" s="29">
         <f>IF(OR(E18="",$D18=""),"",E18*$D18)</f>
         <v/>
       </c>
-      <c r="G18" s="16" t="n"/>
-      <c r="H18" s="17">
+      <c r="G18" s="28" t="n"/>
+      <c r="H18" s="29">
         <f>IF(OR(G18="",$D18=""),"",G18*$D18)</f>
         <v/>
       </c>
-      <c r="I18" s="16" t="n"/>
-      <c r="J18" s="17">
+      <c r="I18" s="28" t="n"/>
+      <c r="J18" s="29">
         <f>IF(OR(I18="",$D18=""),"",I18*$D18)</f>
         <v/>
       </c>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="17">
+      <c r="K18" s="28" t="n"/>
+      <c r="L18" s="29">
         <f>IF(OR(K18="",$D18=""),"",K18*$D18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="9" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="17">
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="29">
         <f>IF(OR(E19="",$D19=""),"",E19*$D19)</f>
         <v/>
       </c>
-      <c r="G19" s="16" t="n"/>
-      <c r="H19" s="17">
+      <c r="G19" s="28" t="n"/>
+      <c r="H19" s="29">
         <f>IF(OR(G19="",$D19=""),"",G19*$D19)</f>
         <v/>
       </c>
-      <c r="I19" s="16" t="n"/>
-      <c r="J19" s="17">
+      <c r="I19" s="28" t="n"/>
+      <c r="J19" s="29">
         <f>IF(OR(I19="",$D19=""),"",I19*$D19)</f>
         <v/>
       </c>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="17">
+      <c r="K19" s="28" t="n"/>
+      <c r="L19" s="29">
         <f>IF(OR(K19="",$D19=""),"",K19*$D19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="11" t="n">
         <v>13</v>
       </c>
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="9" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="17">
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="28" t="n"/>
+      <c r="F20" s="29">
         <f>IF(OR(E20="",$D20=""),"",E20*$D20)</f>
         <v/>
       </c>
-      <c r="G20" s="16" t="n"/>
-      <c r="H20" s="17">
+      <c r="G20" s="28" t="n"/>
+      <c r="H20" s="29">
         <f>IF(OR(G20="",$D20=""),"",G20*$D20)</f>
         <v/>
       </c>
-      <c r="I20" s="16" t="n"/>
-      <c r="J20" s="17">
+      <c r="I20" s="28" t="n"/>
+      <c r="J20" s="29">
         <f>IF(OR(I20="",$D20=""),"",I20*$D20)</f>
         <v/>
       </c>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="17">
+      <c r="K20" s="28" t="n"/>
+      <c r="L20" s="29">
         <f>IF(OR(K20="",$D20=""),"",K20*$D20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="11" t="n">
         <v>14</v>
       </c>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="9" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="17">
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="28" t="n"/>
+      <c r="F21" s="29">
         <f>IF(OR(E21="",$D21=""),"",E21*$D21)</f>
         <v/>
       </c>
-      <c r="G21" s="16" t="n"/>
-      <c r="H21" s="17">
+      <c r="G21" s="28" t="n"/>
+      <c r="H21" s="29">
         <f>IF(OR(G21="",$D21=""),"",G21*$D21)</f>
         <v/>
       </c>
-      <c r="I21" s="16" t="n"/>
-      <c r="J21" s="17">
+      <c r="I21" s="28" t="n"/>
+      <c r="J21" s="29">
         <f>IF(OR(I21="",$D21=""),"",I21*$D21)</f>
         <v/>
       </c>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="17">
+      <c r="K21" s="28" t="n"/>
+      <c r="L21" s="29">
         <f>IF(OR(K21="",$D21=""),"",K21*$D21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="11" t="n">
         <v>15</v>
       </c>
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="9" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="17">
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="29">
         <f>IF(OR(E22="",$D22=""),"",E22*$D22)</f>
         <v/>
       </c>
-      <c r="G22" s="16" t="n"/>
-      <c r="H22" s="17">
+      <c r="G22" s="28" t="n"/>
+      <c r="H22" s="29">
         <f>IF(OR(G22="",$D22=""),"",G22*$D22)</f>
         <v/>
       </c>
-      <c r="I22" s="16" t="n"/>
-      <c r="J22" s="17">
+      <c r="I22" s="28" t="n"/>
+      <c r="J22" s="29">
         <f>IF(OR(I22="",$D22=""),"",I22*$D22)</f>
         <v/>
       </c>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="17">
+      <c r="K22" s="28" t="n"/>
+      <c r="L22" s="29">
         <f>IF(OR(K22="",$D22=""),"",K22*$D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="31">
         <f>SUM(F8:F22)</f>
         <v/>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="31">
         <f>SUM(H8:H22)</f>
         <v/>
       </c>
-      <c r="J23" s="19">
+      <c r="J23" s="31">
         <f>SUM(J8:J22)</f>
         <v/>
       </c>
-      <c r="L23" s="19">
+      <c r="L23" s="31">
         <f>SUM(L8:L22)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>IVA 16%</t>
         </is>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="31">
         <f>ROUND(F23*0.16,2)</f>
         <v/>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="31">
         <f>ROUND(H23*0.16,2)</f>
         <v/>
       </c>
-      <c r="J24" s="19">
+      <c r="J24" s="31">
         <f>ROUND(J23*0.16,2)</f>
         <v/>
       </c>
-      <c r="L24" s="19">
+      <c r="L24" s="31">
         <f>ROUND(L23*0.16,2)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="31">
         <f>F23+F24</f>
         <v/>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="31">
         <f>H23+H24</f>
         <v/>
       </c>
-      <c r="J25" s="19">
+      <c r="J25" s="31">
         <f>J23+J24</f>
         <v/>
       </c>
-      <c r="L25" s="19">
+      <c r="L25" s="31">
         <f>L23+L24</f>
         <v/>
       </c>
@@ -1224,18 +1494,18 @@
       <c r="L27" s="9" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>MEJOR OPCIÓN (menor total)</t>
         </is>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="30">
         <f>IF(MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25))=1E+99,"",IF(F25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),E6,IF(H25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),G6,IF(J25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),I6,IF(L25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),K6,"")))))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>Nota: si un proveedor no cotiza todas las partidas, su total no es comparable.</t>
         </is>
@@ -1255,95 +1525,14 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="22" t="inlineStr">
-        <is>
-          <t>Cuadro comparativo</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="23" t="inlineStr">
-        <is>
-          <t>Guía de uso</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="24" t="inlineStr">
-        <is>
-          <t>Renombra los proveedores en la fila 6.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>Captura descripción, unidad y cantidad de cada partida y el precio unitario ofrecido por proveedor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>Importes, IVA y total se calculan; abajo se indica el proveedor con el menor total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>Anota condiciones de pago y tiempos de entrega, pues el precio no es el único criterio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas amarillas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="25" t="inlineStr">
-        <is>
-          <t>Celdas amarillas = captura · Celdas grises = cálculo automático (no modificar).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 Página &amp;P&amp;R&amp;8 Impreso: &amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/plantillas/3_Inventarios_y_Compras/04_Cuadro_Comparativo_de_Cotizaciones.xlsx
+++ b/plantillas/3_Inventarios_y_Compras/04_Cuadro_Comparativo_de_Cotizaciones.xlsx
@@ -222,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -236,7 +236,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -256,16 +258,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -706,6 +718,7 @@
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="6" t="inlineStr">
         <is>
@@ -763,6 +776,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
@@ -794,6 +808,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="13" t="n"/>
       <c r="B22" s="13" t="n"/>
@@ -808,6 +823,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
@@ -878,6 +894,7 @@
       <c r="K2" s="20" t="n"/>
       <c r="L2" s="21" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="22" t="inlineStr">
         <is>
@@ -894,6 +911,7 @@
       <c r="F4" s="23" t="n"/>
       <c r="G4" s="9" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="E6" s="24" t="inlineStr">
         <is>
@@ -983,490 +1001,490 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="27" t="n">
         <v>1</v>
       </c>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="9" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="28" t="n"/>
-      <c r="F8" s="29">
+      <c r="D8" s="28" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="30">
         <f>IF(OR(E8="",$D8=""),"",E8*$D8)</f>
         <v/>
       </c>
-      <c r="G8" s="28" t="n"/>
-      <c r="H8" s="29">
+      <c r="G8" s="29" t="n"/>
+      <c r="H8" s="30">
         <f>IF(OR(G8="",$D8=""),"",G8*$D8)</f>
         <v/>
       </c>
-      <c r="I8" s="28" t="n"/>
-      <c r="J8" s="29">
+      <c r="I8" s="29" t="n"/>
+      <c r="J8" s="30">
         <f>IF(OR(I8="",$D8=""),"",I8*$D8)</f>
         <v/>
       </c>
-      <c r="K8" s="28" t="n"/>
-      <c r="L8" s="29">
+      <c r="K8" s="29" t="n"/>
+      <c r="L8" s="30">
         <f>IF(OR(K8="",$D8=""),"",K8*$D8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="27" t="n">
         <v>2</v>
       </c>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="9" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="28" t="n"/>
-      <c r="F9" s="29">
+      <c r="D9" s="28" t="n"/>
+      <c r="E9" s="29" t="n"/>
+      <c r="F9" s="30">
         <f>IF(OR(E9="",$D9=""),"",E9*$D9)</f>
         <v/>
       </c>
-      <c r="G9" s="28" t="n"/>
-      <c r="H9" s="29">
+      <c r="G9" s="29" t="n"/>
+      <c r="H9" s="30">
         <f>IF(OR(G9="",$D9=""),"",G9*$D9)</f>
         <v/>
       </c>
-      <c r="I9" s="28" t="n"/>
-      <c r="J9" s="29">
+      <c r="I9" s="29" t="n"/>
+      <c r="J9" s="30">
         <f>IF(OR(I9="",$D9=""),"",I9*$D9)</f>
         <v/>
       </c>
-      <c r="K9" s="28" t="n"/>
-      <c r="L9" s="29">
+      <c r="K9" s="29" t="n"/>
+      <c r="L9" s="30">
         <f>IF(OR(K9="",$D9=""),"",K9*$D9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="27" t="n">
         <v>3</v>
       </c>
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="9" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="28" t="n"/>
-      <c r="F10" s="29">
+      <c r="D10" s="28" t="n"/>
+      <c r="E10" s="29" t="n"/>
+      <c r="F10" s="30">
         <f>IF(OR(E10="",$D10=""),"",E10*$D10)</f>
         <v/>
       </c>
-      <c r="G10" s="28" t="n"/>
-      <c r="H10" s="29">
+      <c r="G10" s="29" t="n"/>
+      <c r="H10" s="30">
         <f>IF(OR(G10="",$D10=""),"",G10*$D10)</f>
         <v/>
       </c>
-      <c r="I10" s="28" t="n"/>
-      <c r="J10" s="29">
+      <c r="I10" s="29" t="n"/>
+      <c r="J10" s="30">
         <f>IF(OR(I10="",$D10=""),"",I10*$D10)</f>
         <v/>
       </c>
-      <c r="K10" s="28" t="n"/>
-      <c r="L10" s="29">
+      <c r="K10" s="29" t="n"/>
+      <c r="L10" s="30">
         <f>IF(OR(K10="",$D10=""),"",K10*$D10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="27" t="n">
         <v>4</v>
       </c>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="9" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="28" t="n"/>
-      <c r="F11" s="29">
+      <c r="D11" s="28" t="n"/>
+      <c r="E11" s="29" t="n"/>
+      <c r="F11" s="30">
         <f>IF(OR(E11="",$D11=""),"",E11*$D11)</f>
         <v/>
       </c>
-      <c r="G11" s="28" t="n"/>
-      <c r="H11" s="29">
+      <c r="G11" s="29" t="n"/>
+      <c r="H11" s="30">
         <f>IF(OR(G11="",$D11=""),"",G11*$D11)</f>
         <v/>
       </c>
-      <c r="I11" s="28" t="n"/>
-      <c r="J11" s="29">
+      <c r="I11" s="29" t="n"/>
+      <c r="J11" s="30">
         <f>IF(OR(I11="",$D11=""),"",I11*$D11)</f>
         <v/>
       </c>
-      <c r="K11" s="28" t="n"/>
-      <c r="L11" s="29">
+      <c r="K11" s="29" t="n"/>
+      <c r="L11" s="30">
         <f>IF(OR(K11="",$D11=""),"",K11*$D11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="27" t="n">
         <v>5</v>
       </c>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="9" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="28" t="n"/>
-      <c r="F12" s="29">
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="29" t="n"/>
+      <c r="F12" s="30">
         <f>IF(OR(E12="",$D12=""),"",E12*$D12)</f>
         <v/>
       </c>
-      <c r="G12" s="28" t="n"/>
-      <c r="H12" s="29">
+      <c r="G12" s="29" t="n"/>
+      <c r="H12" s="30">
         <f>IF(OR(G12="",$D12=""),"",G12*$D12)</f>
         <v/>
       </c>
-      <c r="I12" s="28" t="n"/>
-      <c r="J12" s="29">
+      <c r="I12" s="29" t="n"/>
+      <c r="J12" s="30">
         <f>IF(OR(I12="",$D12=""),"",I12*$D12)</f>
         <v/>
       </c>
-      <c r="K12" s="28" t="n"/>
-      <c r="L12" s="29">
+      <c r="K12" s="29" t="n"/>
+      <c r="L12" s="30">
         <f>IF(OR(K12="",$D12=""),"",K12*$D12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="27" t="n">
         <v>6</v>
       </c>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="9" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="28" t="n"/>
-      <c r="F13" s="29">
+      <c r="D13" s="28" t="n"/>
+      <c r="E13" s="29" t="n"/>
+      <c r="F13" s="30">
         <f>IF(OR(E13="",$D13=""),"",E13*$D13)</f>
         <v/>
       </c>
-      <c r="G13" s="28" t="n"/>
-      <c r="H13" s="29">
+      <c r="G13" s="29" t="n"/>
+      <c r="H13" s="30">
         <f>IF(OR(G13="",$D13=""),"",G13*$D13)</f>
         <v/>
       </c>
-      <c r="I13" s="28" t="n"/>
-      <c r="J13" s="29">
+      <c r="I13" s="29" t="n"/>
+      <c r="J13" s="30">
         <f>IF(OR(I13="",$D13=""),"",I13*$D13)</f>
         <v/>
       </c>
-      <c r="K13" s="28" t="n"/>
-      <c r="L13" s="29">
+      <c r="K13" s="29" t="n"/>
+      <c r="L13" s="30">
         <f>IF(OR(K13="",$D13=""),"",K13*$D13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="27" t="n">
         <v>7</v>
       </c>
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="9" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="28" t="n"/>
-      <c r="F14" s="29">
+      <c r="D14" s="28" t="n"/>
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="30">
         <f>IF(OR(E14="",$D14=""),"",E14*$D14)</f>
         <v/>
       </c>
-      <c r="G14" s="28" t="n"/>
-      <c r="H14" s="29">
+      <c r="G14" s="29" t="n"/>
+      <c r="H14" s="30">
         <f>IF(OR(G14="",$D14=""),"",G14*$D14)</f>
         <v/>
       </c>
-      <c r="I14" s="28" t="n"/>
-      <c r="J14" s="29">
+      <c r="I14" s="29" t="n"/>
+      <c r="J14" s="30">
         <f>IF(OR(I14="",$D14=""),"",I14*$D14)</f>
         <v/>
       </c>
-      <c r="K14" s="28" t="n"/>
-      <c r="L14" s="29">
+      <c r="K14" s="29" t="n"/>
+      <c r="L14" s="30">
         <f>IF(OR(K14="",$D14=""),"",K14*$D14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="27" t="n">
         <v>8</v>
       </c>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="9" t="n"/>
-      <c r="D15" s="27" t="n"/>
-      <c r="E15" s="28" t="n"/>
-      <c r="F15" s="29">
+      <c r="D15" s="28" t="n"/>
+      <c r="E15" s="29" t="n"/>
+      <c r="F15" s="30">
         <f>IF(OR(E15="",$D15=""),"",E15*$D15)</f>
         <v/>
       </c>
-      <c r="G15" s="28" t="n"/>
-      <c r="H15" s="29">
+      <c r="G15" s="29" t="n"/>
+      <c r="H15" s="30">
         <f>IF(OR(G15="",$D15=""),"",G15*$D15)</f>
         <v/>
       </c>
-      <c r="I15" s="28" t="n"/>
-      <c r="J15" s="29">
+      <c r="I15" s="29" t="n"/>
+      <c r="J15" s="30">
         <f>IF(OR(I15="",$D15=""),"",I15*$D15)</f>
         <v/>
       </c>
-      <c r="K15" s="28" t="n"/>
-      <c r="L15" s="29">
+      <c r="K15" s="29" t="n"/>
+      <c r="L15" s="30">
         <f>IF(OR(K15="",$D15=""),"",K15*$D15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="27" t="n">
         <v>9</v>
       </c>
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="9" t="n"/>
-      <c r="D16" s="27" t="n"/>
-      <c r="E16" s="28" t="n"/>
-      <c r="F16" s="29">
+      <c r="D16" s="28" t="n"/>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="30">
         <f>IF(OR(E16="",$D16=""),"",E16*$D16)</f>
         <v/>
       </c>
-      <c r="G16" s="28" t="n"/>
-      <c r="H16" s="29">
+      <c r="G16" s="29" t="n"/>
+      <c r="H16" s="30">
         <f>IF(OR(G16="",$D16=""),"",G16*$D16)</f>
         <v/>
       </c>
-      <c r="I16" s="28" t="n"/>
-      <c r="J16" s="29">
+      <c r="I16" s="29" t="n"/>
+      <c r="J16" s="30">
         <f>IF(OR(I16="",$D16=""),"",I16*$D16)</f>
         <v/>
       </c>
-      <c r="K16" s="28" t="n"/>
-      <c r="L16" s="29">
+      <c r="K16" s="29" t="n"/>
+      <c r="L16" s="30">
         <f>IF(OR(K16="",$D16=""),"",K16*$D16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="27" t="n">
         <v>10</v>
       </c>
       <c r="B17" s="9" t="n"/>
       <c r="C17" s="9" t="n"/>
-      <c r="D17" s="27" t="n"/>
-      <c r="E17" s="28" t="n"/>
-      <c r="F17" s="29">
+      <c r="D17" s="28" t="n"/>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="30">
         <f>IF(OR(E17="",$D17=""),"",E17*$D17)</f>
         <v/>
       </c>
-      <c r="G17" s="28" t="n"/>
-      <c r="H17" s="29">
+      <c r="G17" s="29" t="n"/>
+      <c r="H17" s="30">
         <f>IF(OR(G17="",$D17=""),"",G17*$D17)</f>
         <v/>
       </c>
-      <c r="I17" s="28" t="n"/>
-      <c r="J17" s="29">
+      <c r="I17" s="29" t="n"/>
+      <c r="J17" s="30">
         <f>IF(OR(I17="",$D17=""),"",I17*$D17)</f>
         <v/>
       </c>
-      <c r="K17" s="28" t="n"/>
-      <c r="L17" s="29">
+      <c r="K17" s="29" t="n"/>
+      <c r="L17" s="30">
         <f>IF(OR(K17="",$D17=""),"",K17*$D17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="27" t="n">
         <v>11</v>
       </c>
       <c r="B18" s="9" t="n"/>
       <c r="C18" s="9" t="n"/>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="28" t="n"/>
-      <c r="F18" s="29">
+      <c r="D18" s="28" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="30">
         <f>IF(OR(E18="",$D18=""),"",E18*$D18)</f>
         <v/>
       </c>
-      <c r="G18" s="28" t="n"/>
-      <c r="H18" s="29">
+      <c r="G18" s="29" t="n"/>
+      <c r="H18" s="30">
         <f>IF(OR(G18="",$D18=""),"",G18*$D18)</f>
         <v/>
       </c>
-      <c r="I18" s="28" t="n"/>
-      <c r="J18" s="29">
+      <c r="I18" s="29" t="n"/>
+      <c r="J18" s="30">
         <f>IF(OR(I18="",$D18=""),"",I18*$D18)</f>
         <v/>
       </c>
-      <c r="K18" s="28" t="n"/>
-      <c r="L18" s="29">
+      <c r="K18" s="29" t="n"/>
+      <c r="L18" s="30">
         <f>IF(OR(K18="",$D18=""),"",K18*$D18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="27" t="n">
         <v>12</v>
       </c>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="9" t="n"/>
-      <c r="D19" s="27" t="n"/>
-      <c r="E19" s="28" t="n"/>
-      <c r="F19" s="29">
+      <c r="D19" s="28" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="30">
         <f>IF(OR(E19="",$D19=""),"",E19*$D19)</f>
         <v/>
       </c>
-      <c r="G19" s="28" t="n"/>
-      <c r="H19" s="29">
+      <c r="G19" s="29" t="n"/>
+      <c r="H19" s="30">
         <f>IF(OR(G19="",$D19=""),"",G19*$D19)</f>
         <v/>
       </c>
-      <c r="I19" s="28" t="n"/>
-      <c r="J19" s="29">
+      <c r="I19" s="29" t="n"/>
+      <c r="J19" s="30">
         <f>IF(OR(I19="",$D19=""),"",I19*$D19)</f>
         <v/>
       </c>
-      <c r="K19" s="28" t="n"/>
-      <c r="L19" s="29">
+      <c r="K19" s="29" t="n"/>
+      <c r="L19" s="30">
         <f>IF(OR(K19="",$D19=""),"",K19*$D19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="27" t="n">
         <v>13</v>
       </c>
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="9" t="n"/>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="28" t="n"/>
-      <c r="F20" s="29">
+      <c r="D20" s="28" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="30">
         <f>IF(OR(E20="",$D20=""),"",E20*$D20)</f>
         <v/>
       </c>
-      <c r="G20" s="28" t="n"/>
-      <c r="H20" s="29">
+      <c r="G20" s="29" t="n"/>
+      <c r="H20" s="30">
         <f>IF(OR(G20="",$D20=""),"",G20*$D20)</f>
         <v/>
       </c>
-      <c r="I20" s="28" t="n"/>
-      <c r="J20" s="29">
+      <c r="I20" s="29" t="n"/>
+      <c r="J20" s="30">
         <f>IF(OR(I20="",$D20=""),"",I20*$D20)</f>
         <v/>
       </c>
-      <c r="K20" s="28" t="n"/>
-      <c r="L20" s="29">
+      <c r="K20" s="29" t="n"/>
+      <c r="L20" s="30">
         <f>IF(OR(K20="",$D20=""),"",K20*$D20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="27" t="n">
         <v>14</v>
       </c>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="9" t="n"/>
-      <c r="D21" s="27" t="n"/>
-      <c r="E21" s="28" t="n"/>
-      <c r="F21" s="29">
+      <c r="D21" s="28" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="30">
         <f>IF(OR(E21="",$D21=""),"",E21*$D21)</f>
         <v/>
       </c>
-      <c r="G21" s="28" t="n"/>
-      <c r="H21" s="29">
+      <c r="G21" s="29" t="n"/>
+      <c r="H21" s="30">
         <f>IF(OR(G21="",$D21=""),"",G21*$D21)</f>
         <v/>
       </c>
-      <c r="I21" s="28" t="n"/>
-      <c r="J21" s="29">
+      <c r="I21" s="29" t="n"/>
+      <c r="J21" s="30">
         <f>IF(OR(I21="",$D21=""),"",I21*$D21)</f>
         <v/>
       </c>
-      <c r="K21" s="28" t="n"/>
-      <c r="L21" s="29">
+      <c r="K21" s="29" t="n"/>
+      <c r="L21" s="30">
         <f>IF(OR(K21="",$D21=""),"",K21*$D21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="27" t="n">
         <v>15</v>
       </c>
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="9" t="n"/>
-      <c r="D22" s="27" t="n"/>
-      <c r="E22" s="28" t="n"/>
-      <c r="F22" s="29">
+      <c r="D22" s="28" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="30">
         <f>IF(OR(E22="",$D22=""),"",E22*$D22)</f>
         <v/>
       </c>
-      <c r="G22" s="28" t="n"/>
-      <c r="H22" s="29">
+      <c r="G22" s="29" t="n"/>
+      <c r="H22" s="30">
         <f>IF(OR(G22="",$D22=""),"",G22*$D22)</f>
         <v/>
       </c>
-      <c r="I22" s="28" t="n"/>
-      <c r="J22" s="29">
+      <c r="I22" s="29" t="n"/>
+      <c r="J22" s="30">
         <f>IF(OR(I22="",$D22=""),"",I22*$D22)</f>
         <v/>
       </c>
-      <c r="K22" s="28" t="n"/>
-      <c r="L22" s="29">
+      <c r="K22" s="29" t="n"/>
+      <c r="L22" s="30">
         <f>IF(OR(K22="",$D22=""),"",K22*$D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="30" t="inlineStr">
+      <c r="B23" s="31" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="F23" s="31">
+      <c r="F23" s="32">
         <f>SUM(F8:F22)</f>
         <v/>
       </c>
-      <c r="H23" s="31">
+      <c r="H23" s="32">
         <f>SUM(H8:H22)</f>
         <v/>
       </c>
-      <c r="J23" s="31">
+      <c r="J23" s="32">
         <f>SUM(J8:J22)</f>
         <v/>
       </c>
-      <c r="L23" s="31">
+      <c r="L23" s="32">
         <f>SUM(L8:L22)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>IVA 16%</t>
         </is>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <f>ROUND(F23*0.16,2)</f>
         <v/>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="32">
         <f>ROUND(H23*0.16,2)</f>
         <v/>
       </c>
-      <c r="J24" s="31">
+      <c r="J24" s="32">
         <f>ROUND(J23*0.16,2)</f>
         <v/>
       </c>
-      <c r="L24" s="31">
+      <c r="L24" s="32">
         <f>ROUND(L23*0.16,2)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="30" t="inlineStr">
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="32">
         <f>F23+F24</f>
         <v/>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="32">
         <f>H23+H24</f>
         <v/>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="32">
         <f>J23+J24</f>
         <v/>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="32">
         <f>L23+L24</f>
         <v/>
       </c>
@@ -1493,25 +1511,27 @@
       <c r="J27" s="9" t="n"/>
       <c r="L27" s="9" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29">
-      <c r="B29" s="32" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>MEJOR OPCIÓN (menor total)</t>
         </is>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="31">
         <f>IF(MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25))=1E+99,"",IF(F25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),E6,IF(H25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),G6,IF(J25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),I6,IF(L25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),K6,"")))))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="33" t="inlineStr">
+      <c r="B30" s="34" t="inlineStr">
         <is>
           <t>Nota: si un proveedor no cotiza todas las partidas, su total no es comparable.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="9">
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="A1:J1"/>

--- a/plantillas/3_Inventarios_y_Compras/04_Cuadro_Comparativo_de_Cotizaciones.xlsx
+++ b/plantillas/3_Inventarios_y_Compras/04_Cuadro_Comparativo_de_Cotizaciones.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formato" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PORTADA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FORMATO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMEN" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYUDA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.##"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,88 +33,153 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="20"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <i val="1"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <i val="1"/>
       <color rgb="00A6A6A6"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="001B6B73"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <i val="1"/>
       <color rgb="007F7F7F"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="000B2A4A"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="30"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <i val="1"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="000B2A4A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="002B2B2B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="005B6B78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="26"/>
+      <color rgb="001B6B73"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="00C9D3DB"/>
+      <name val="Abadi"/>
+      <color rgb="000B2A4A"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001B6B73"/>
+      <name val="Abadi"/>
+      <color theme="1"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00C9A227"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="002B2B2B"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="005B6B78"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="008A97A3"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -139,8 +206,13 @@
         <fgColor rgb="00EEF2F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -209,80 +281,189 @@
       </bottom>
     </border>
     <border>
+      <top style="dashed">
+        <color rgb="00A6A6A6"/>
+      </top>
+    </border>
+    <border>
+      <bottom style="dashed">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3DB"/>
+      </left>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3DB"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9A227"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9A227"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9A227"/>
+      </bottom>
+    </border>
+    <border>
       <top style="thick">
         <color rgb="00C9A227"/>
       </top>
     </border>
     <border>
-      <top style="thin">
-        <color rgb="00C9A227"/>
-      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="26" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="26" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="26" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="26" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="9" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -357,6 +538,120 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Total por proveedor (con IVA)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'RESUMEN'!C25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1B6B73"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1B6B73"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'RESUMEN'!$B$26:$B$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'RESUMEN'!$C$26:$C$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8460000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -649,22 +944,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="88" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="8" customHeight="1">
       <c r="A1" s="1" t="n"/>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -673,157 +974,513 @@
       </c>
       <c r="C2" s="1" t="n"/>
       <c r="D2" s="1" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>VERSIÓN 2.0  ·  MÉXICO</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="1" t="n"/>
       <c r="C3" s="1" t="n"/>
       <c r="D3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="40" customHeight="1">
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Cuadro comparativo</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-    </row>
-    <row r="5">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>CUADRO COMPARATIVO</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="1" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Formato administrativo editable · México</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-    </row>
-    <row r="6">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="1" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="1" t="n"/>
-      <c r="C6" s="1" t="n"/>
-      <c r="D6" s="1" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Formato administrativo profesional · editable · listo para imprimir</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="1" t="n"/>
       <c r="D7" s="1" t="n"/>
-    </row>
-    <row r="8" ht="6" customHeight="1">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-    </row>
-    <row r="9"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="n"/>
+      <c r="G7" s="1" t="n"/>
+    </row>
+    <row r="8" ht="4" customHeight="1">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="1" t="n"/>
+      <c r="G8" s="1" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>FÓRMULAS AUTOMÁTICAS</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>LISTAS DESPLEGABLES</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>HOJAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>LISTO PARA IMPRIMIR</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="n"/>
+    </row>
     <row r="10">
-      <c r="B10" s="6" t="inlineStr">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="n"/>
+      <c r="D10" s="1" t="n"/>
+      <c r="E10" s="1" t="n"/>
+      <c r="F10" s="1" t="n"/>
+      <c r="G10" s="1" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="1" t="n"/>
+      <c r="D11" s="1" t="n"/>
+      <c r="E11" s="1" t="n"/>
+      <c r="F11" s="1" t="n"/>
+      <c r="G11" s="1" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="n"/>
+      <c r="D12" s="1" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
+    </row>
+    <row r="13" ht="6" customHeight="1">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>¿QUÉ INCLUYE ESTE ARCHIVO?</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>▸</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>FORMATO</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Hoja principal de captura. Aquí registras tu información; las celdas grises calculan solas.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>▸</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>RESUMEN</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Tablero con indicadores y gráficas que se actualizan automáticamente con tus datos.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>▸</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>AYUDA</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Preguntas frecuentes, glosario y lista de verificación para cerrar tu periodo.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>CÓMO USARLO</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="21" customHeight="1">
-      <c r="B11" s="7" t="n">
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Renombra los proveedores en la fila 6.</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="B12" s="7" t="n">
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="21" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Captura descripción, unidad y cantidad de cada partida y el precio unitario ofrecido por proveedor.</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="21" customHeight="1">
-      <c r="B13" s="7" t="n">
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Importes, IVA y total se calculan; abajo se indica el proveedor con el menor total.</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="B14" s="7" t="n">
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Anota condiciones de pago y tiempos de entrega, pues el precio no es el único criterio.</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="B15" s="7" t="n">
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>LEYENDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="9" t="inlineStr"/>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Celda de captura: escribe aquí.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="11" t="inlineStr"/>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Cálculo automático: no la modifiques.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="12" t="inlineStr"/>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Encabezados y títulos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="13" t="n"/>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>GRUPO CANVILLE · Formatos administrativos · v1.0</t>
-        </is>
-      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>RECOMENDACIONES DE USO</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="21" customHeight="1">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Solicita al menos tres cotizaciones con las mismas especificaciones.</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>El precio no es el único criterio: valora calidad, garantía, tiempo de entrega y crédito.</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Si un proveedor no cotiza todas las partidas, no es comparable en el total.</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="21" customHeight="1">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Archiva el cuadro como soporte de la decisión de compra.</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>LEYENDA DE COLORES</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="17" t="inlineStr"/>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>CELDA DE CAPTURA: escribe aquí.</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="19" t="inlineStr"/>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="20" t="inlineStr"/>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>ENCABEZADOS Y TÍTULOS.</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="1" t="n"/>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>GRUPO CANVILLE  ·  Formatos administrativos  ·  Para uso interno de tu empresa</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="1" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="16">
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="B4:F5"/>
+    <mergeCell ref="C28:F28"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
@@ -854,7 +1511,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>CUADRO COMPARATIVO DE COTIZACIONES</t>
         </is>
@@ -868,667 +1525,772 @@
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
-      <c r="K1" s="16" t="inlineStr">
+      <c r="K1" s="23" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="L1" s="17" t="n"/>
+      <c r="L1" s="24" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>Compara hasta 4 proveedores y selecciona la mejor opción</t>
         </is>
       </c>
-      <c r="B2" s="19" t="n"/>
-      <c r="C2" s="19" t="n"/>
-      <c r="D2" s="19" t="n"/>
-      <c r="E2" s="19" t="n"/>
-      <c r="F2" s="19" t="n"/>
-      <c r="G2" s="19" t="n"/>
-      <c r="H2" s="19" t="n"/>
-      <c r="I2" s="19" t="n"/>
-      <c r="J2" s="19" t="n"/>
-      <c r="K2" s="20" t="n"/>
-      <c r="L2" s="21" t="n"/>
-    </row>
-    <row r="3"/>
+      <c r="B2" s="26" t="n"/>
+      <c r="C2" s="26" t="n"/>
+      <c r="D2" s="26" t="n"/>
+      <c r="E2" s="26" t="n"/>
+      <c r="F2" s="26" t="n"/>
+      <c r="G2" s="26" t="n"/>
+      <c r="H2" s="26" t="n"/>
+      <c r="I2" s="26" t="n"/>
+      <c r="J2" s="26" t="n"/>
+      <c r="K2" s="27" t="n"/>
+      <c r="L2" s="28" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
-        <is>
-          <t>Requisición No.</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="F4" s="23" t="n"/>
-      <c r="G4" s="9" t="n"/>
-    </row>
-    <row r="5"/>
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>REQUISICIÓN NO.</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="17" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+    </row>
     <row r="6">
-      <c r="E6" s="24" t="inlineStr">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>Proveedor A</t>
         </is>
       </c>
-      <c r="F6" s="25" t="n"/>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="31" t="inlineStr">
         <is>
           <t>Proveedor B</t>
         </is>
       </c>
-      <c r="H6" s="25" t="n"/>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="H6" s="32" t="n"/>
+      <c r="I6" s="31" t="inlineStr">
         <is>
           <t>Proveedor C</t>
         </is>
       </c>
-      <c r="J6" s="25" t="n"/>
-      <c r="K6" s="24" t="inlineStr">
+      <c r="J6" s="32" t="n"/>
+      <c r="K6" s="31" t="inlineStr">
         <is>
           <t>Proveedor D</t>
         </is>
       </c>
-      <c r="L6" s="25" t="n"/>
+      <c r="L6" s="32" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
-        <is>
-          <t>Part.</t>
-        </is>
-      </c>
-      <c r="B7" s="26" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="C7" s="26" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="D7" s="26" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-      <c r="E7" s="26" t="inlineStr">
-        <is>
-          <t>P. Unit.</t>
-        </is>
-      </c>
-      <c r="F7" s="26" t="inlineStr">
-        <is>
-          <t>Importe</t>
-        </is>
-      </c>
-      <c r="G7" s="26" t="inlineStr">
-        <is>
-          <t>P. Unit.</t>
-        </is>
-      </c>
-      <c r="H7" s="26" t="inlineStr">
-        <is>
-          <t>Importe</t>
-        </is>
-      </c>
-      <c r="I7" s="26" t="inlineStr">
-        <is>
-          <t>P. Unit.</t>
-        </is>
-      </c>
-      <c r="J7" s="26" t="inlineStr">
-        <is>
-          <t>Importe</t>
-        </is>
-      </c>
-      <c r="K7" s="26" t="inlineStr">
-        <is>
-          <t>P. Unit.</t>
-        </is>
-      </c>
-      <c r="L7" s="26" t="inlineStr">
-        <is>
-          <t>Importe</t>
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>PART.</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>UNIDAD</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>CANTIDAD</t>
+        </is>
+      </c>
+      <c r="E7" s="33" t="inlineStr">
+        <is>
+          <t>P. UNIT.</t>
+        </is>
+      </c>
+      <c r="F7" s="33" t="inlineStr">
+        <is>
+          <t>IMPORTE</t>
+        </is>
+      </c>
+      <c r="G7" s="33" t="inlineStr">
+        <is>
+          <t>P. UNIT.</t>
+        </is>
+      </c>
+      <c r="H7" s="33" t="inlineStr">
+        <is>
+          <t>IMPORTE</t>
+        </is>
+      </c>
+      <c r="I7" s="33" t="inlineStr">
+        <is>
+          <t>P. UNIT.</t>
+        </is>
+      </c>
+      <c r="J7" s="33" t="inlineStr">
+        <is>
+          <t>IMPORTE</t>
+        </is>
+      </c>
+      <c r="K7" s="33" t="inlineStr">
+        <is>
+          <t>P. UNIT.</t>
+        </is>
+      </c>
+      <c r="L7" s="33" t="inlineStr">
+        <is>
+          <t>IMPORTE</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="28" t="n"/>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="30">
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="37">
         <f>IF(OR(E8="",$D8=""),"",E8*$D8)</f>
         <v/>
       </c>
-      <c r="G8" s="29" t="n"/>
-      <c r="H8" s="30">
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="37">
         <f>IF(OR(G8="",$D8=""),"",G8*$D8)</f>
         <v/>
       </c>
-      <c r="I8" s="29" t="n"/>
-      <c r="J8" s="30">
+      <c r="I8" s="36" t="n"/>
+      <c r="J8" s="37">
         <f>IF(OR(I8="",$D8=""),"",I8*$D8)</f>
         <v/>
       </c>
-      <c r="K8" s="29" t="n"/>
-      <c r="L8" s="30">
+      <c r="K8" s="36" t="n"/>
+      <c r="L8" s="37">
         <f>IF(OR(K8="",$D8=""),"",K8*$D8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="28" t="n"/>
-      <c r="E9" s="29" t="n"/>
-      <c r="F9" s="30">
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="37">
         <f>IF(OR(E9="",$D9=""),"",E9*$D9)</f>
         <v/>
       </c>
-      <c r="G9" s="29" t="n"/>
-      <c r="H9" s="30">
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="37">
         <f>IF(OR(G9="",$D9=""),"",G9*$D9)</f>
         <v/>
       </c>
-      <c r="I9" s="29" t="n"/>
-      <c r="J9" s="30">
+      <c r="I9" s="36" t="n"/>
+      <c r="J9" s="37">
         <f>IF(OR(I9="",$D9=""),"",I9*$D9)</f>
         <v/>
       </c>
-      <c r="K9" s="29" t="n"/>
-      <c r="L9" s="30">
+      <c r="K9" s="36" t="n"/>
+      <c r="L9" s="37">
         <f>IF(OR(K9="",$D9=""),"",K9*$D9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="28" t="n"/>
-      <c r="E10" s="29" t="n"/>
-      <c r="F10" s="30">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="37">
         <f>IF(OR(E10="",$D10=""),"",E10*$D10)</f>
         <v/>
       </c>
-      <c r="G10" s="29" t="n"/>
-      <c r="H10" s="30">
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="37">
         <f>IF(OR(G10="",$D10=""),"",G10*$D10)</f>
         <v/>
       </c>
-      <c r="I10" s="29" t="n"/>
-      <c r="J10" s="30">
+      <c r="I10" s="36" t="n"/>
+      <c r="J10" s="37">
         <f>IF(OR(I10="",$D10=""),"",I10*$D10)</f>
         <v/>
       </c>
-      <c r="K10" s="29" t="n"/>
-      <c r="L10" s="30">
+      <c r="K10" s="36" t="n"/>
+      <c r="L10" s="37">
         <f>IF(OR(K10="",$D10=""),"",K10*$D10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="n">
+      <c r="A11" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="28" t="n"/>
-      <c r="E11" s="29" t="n"/>
-      <c r="F11" s="30">
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="37">
         <f>IF(OR(E11="",$D11=""),"",E11*$D11)</f>
         <v/>
       </c>
-      <c r="G11" s="29" t="n"/>
-      <c r="H11" s="30">
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="37">
         <f>IF(OR(G11="",$D11=""),"",G11*$D11)</f>
         <v/>
       </c>
-      <c r="I11" s="29" t="n"/>
-      <c r="J11" s="30">
+      <c r="I11" s="36" t="n"/>
+      <c r="J11" s="37">
         <f>IF(OR(I11="",$D11=""),"",I11*$D11)</f>
         <v/>
       </c>
-      <c r="K11" s="29" t="n"/>
-      <c r="L11" s="30">
+      <c r="K11" s="36" t="n"/>
+      <c r="L11" s="37">
         <f>IF(OR(K11="",$D11=""),"",K11*$D11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="n">
+      <c r="A12" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="28" t="n"/>
-      <c r="E12" s="29" t="n"/>
-      <c r="F12" s="30">
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="37">
         <f>IF(OR(E12="",$D12=""),"",E12*$D12)</f>
         <v/>
       </c>
-      <c r="G12" s="29" t="n"/>
-      <c r="H12" s="30">
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="37">
         <f>IF(OR(G12="",$D12=""),"",G12*$D12)</f>
         <v/>
       </c>
-      <c r="I12" s="29" t="n"/>
-      <c r="J12" s="30">
+      <c r="I12" s="36" t="n"/>
+      <c r="J12" s="37">
         <f>IF(OR(I12="",$D12=""),"",I12*$D12)</f>
         <v/>
       </c>
-      <c r="K12" s="29" t="n"/>
-      <c r="L12" s="30">
+      <c r="K12" s="36" t="n"/>
+      <c r="L12" s="37">
         <f>IF(OR(K12="",$D12=""),"",K12*$D12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="n">
+      <c r="A13" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="28" t="n"/>
-      <c r="E13" s="29" t="n"/>
-      <c r="F13" s="30">
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="37">
         <f>IF(OR(E13="",$D13=""),"",E13*$D13)</f>
         <v/>
       </c>
-      <c r="G13" s="29" t="n"/>
-      <c r="H13" s="30">
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="37">
         <f>IF(OR(G13="",$D13=""),"",G13*$D13)</f>
         <v/>
       </c>
-      <c r="I13" s="29" t="n"/>
-      <c r="J13" s="30">
+      <c r="I13" s="36" t="n"/>
+      <c r="J13" s="37">
         <f>IF(OR(I13="",$D13=""),"",I13*$D13)</f>
         <v/>
       </c>
-      <c r="K13" s="29" t="n"/>
-      <c r="L13" s="30">
+      <c r="K13" s="36" t="n"/>
+      <c r="L13" s="37">
         <f>IF(OR(K13="",$D13=""),"",K13*$D13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="28" t="n"/>
-      <c r="E14" s="29" t="n"/>
-      <c r="F14" s="30">
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="37">
         <f>IF(OR(E14="",$D14=""),"",E14*$D14)</f>
         <v/>
       </c>
-      <c r="G14" s="29" t="n"/>
-      <c r="H14" s="30">
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="37">
         <f>IF(OR(G14="",$D14=""),"",G14*$D14)</f>
         <v/>
       </c>
-      <c r="I14" s="29" t="n"/>
-      <c r="J14" s="30">
+      <c r="I14" s="36" t="n"/>
+      <c r="J14" s="37">
         <f>IF(OR(I14="",$D14=""),"",I14*$D14)</f>
         <v/>
       </c>
-      <c r="K14" s="29" t="n"/>
-      <c r="L14" s="30">
+      <c r="K14" s="36" t="n"/>
+      <c r="L14" s="37">
         <f>IF(OR(K14="",$D14=""),"",K14*$D14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="29" t="n"/>
-      <c r="F15" s="30">
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="37">
         <f>IF(OR(E15="",$D15=""),"",E15*$D15)</f>
         <v/>
       </c>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="30">
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="37">
         <f>IF(OR(G15="",$D15=""),"",G15*$D15)</f>
         <v/>
       </c>
-      <c r="I15" s="29" t="n"/>
-      <c r="J15" s="30">
+      <c r="I15" s="36" t="n"/>
+      <c r="J15" s="37">
         <f>IF(OR(I15="",$D15=""),"",I15*$D15)</f>
         <v/>
       </c>
-      <c r="K15" s="29" t="n"/>
-      <c r="L15" s="30">
+      <c r="K15" s="36" t="n"/>
+      <c r="L15" s="37">
         <f>IF(OR(K15="",$D15=""),"",K15*$D15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="28" t="n"/>
-      <c r="E16" s="29" t="n"/>
-      <c r="F16" s="30">
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="37">
         <f>IF(OR(E16="",$D16=""),"",E16*$D16)</f>
         <v/>
       </c>
-      <c r="G16" s="29" t="n"/>
-      <c r="H16" s="30">
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="37">
         <f>IF(OR(G16="",$D16=""),"",G16*$D16)</f>
         <v/>
       </c>
-      <c r="I16" s="29" t="n"/>
-      <c r="J16" s="30">
+      <c r="I16" s="36" t="n"/>
+      <c r="J16" s="37">
         <f>IF(OR(I16="",$D16=""),"",I16*$D16)</f>
         <v/>
       </c>
-      <c r="K16" s="29" t="n"/>
-      <c r="L16" s="30">
+      <c r="K16" s="36" t="n"/>
+      <c r="L16" s="37">
         <f>IF(OR(K16="",$D16=""),"",K16*$D16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="n">
+      <c r="A17" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="28" t="n"/>
-      <c r="E17" s="29" t="n"/>
-      <c r="F17" s="30">
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="37">
         <f>IF(OR(E17="",$D17=""),"",E17*$D17)</f>
         <v/>
       </c>
-      <c r="G17" s="29" t="n"/>
-      <c r="H17" s="30">
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="37">
         <f>IF(OR(G17="",$D17=""),"",G17*$D17)</f>
         <v/>
       </c>
-      <c r="I17" s="29" t="n"/>
-      <c r="J17" s="30">
+      <c r="I17" s="36" t="n"/>
+      <c r="J17" s="37">
         <f>IF(OR(I17="",$D17=""),"",I17*$D17)</f>
         <v/>
       </c>
-      <c r="K17" s="29" t="n"/>
-      <c r="L17" s="30">
+      <c r="K17" s="36" t="n"/>
+      <c r="L17" s="37">
         <f>IF(OR(K17="",$D17=""),"",K17*$D17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="n">
+      <c r="A18" s="34" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="28" t="n"/>
-      <c r="E18" s="29" t="n"/>
-      <c r="F18" s="30">
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="37">
         <f>IF(OR(E18="",$D18=""),"",E18*$D18)</f>
         <v/>
       </c>
-      <c r="G18" s="29" t="n"/>
-      <c r="H18" s="30">
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="37">
         <f>IF(OR(G18="",$D18=""),"",G18*$D18)</f>
         <v/>
       </c>
-      <c r="I18" s="29" t="n"/>
-      <c r="J18" s="30">
+      <c r="I18" s="36" t="n"/>
+      <c r="J18" s="37">
         <f>IF(OR(I18="",$D18=""),"",I18*$D18)</f>
         <v/>
       </c>
-      <c r="K18" s="29" t="n"/>
-      <c r="L18" s="30">
+      <c r="K18" s="36" t="n"/>
+      <c r="L18" s="37">
         <f>IF(OR(K18="",$D18=""),"",K18*$D18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="n">
+      <c r="A19" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="28" t="n"/>
-      <c r="E19" s="29" t="n"/>
-      <c r="F19" s="30">
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="37">
         <f>IF(OR(E19="",$D19=""),"",E19*$D19)</f>
         <v/>
       </c>
-      <c r="G19" s="29" t="n"/>
-      <c r="H19" s="30">
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="37">
         <f>IF(OR(G19="",$D19=""),"",G19*$D19)</f>
         <v/>
       </c>
-      <c r="I19" s="29" t="n"/>
-      <c r="J19" s="30">
+      <c r="I19" s="36" t="n"/>
+      <c r="J19" s="37">
         <f>IF(OR(I19="",$D19=""),"",I19*$D19)</f>
         <v/>
       </c>
-      <c r="K19" s="29" t="n"/>
-      <c r="L19" s="30">
+      <c r="K19" s="36" t="n"/>
+      <c r="L19" s="37">
         <f>IF(OR(K19="",$D19=""),"",K19*$D19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n">
+      <c r="A20" s="34" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="28" t="n"/>
-      <c r="E20" s="29" t="n"/>
-      <c r="F20" s="30">
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="37">
         <f>IF(OR(E20="",$D20=""),"",E20*$D20)</f>
         <v/>
       </c>
-      <c r="G20" s="29" t="n"/>
-      <c r="H20" s="30">
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="37">
         <f>IF(OR(G20="",$D20=""),"",G20*$D20)</f>
         <v/>
       </c>
-      <c r="I20" s="29" t="n"/>
-      <c r="J20" s="30">
+      <c r="I20" s="36" t="n"/>
+      <c r="J20" s="37">
         <f>IF(OR(I20="",$D20=""),"",I20*$D20)</f>
         <v/>
       </c>
-      <c r="K20" s="29" t="n"/>
-      <c r="L20" s="30">
+      <c r="K20" s="36" t="n"/>
+      <c r="L20" s="37">
         <f>IF(OR(K20="",$D20=""),"",K20*$D20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="n">
+      <c r="A21" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="28" t="n"/>
-      <c r="E21" s="29" t="n"/>
-      <c r="F21" s="30">
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="37">
         <f>IF(OR(E21="",$D21=""),"",E21*$D21)</f>
         <v/>
       </c>
-      <c r="G21" s="29" t="n"/>
-      <c r="H21" s="30">
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="37">
         <f>IF(OR(G21="",$D21=""),"",G21*$D21)</f>
         <v/>
       </c>
-      <c r="I21" s="29" t="n"/>
-      <c r="J21" s="30">
+      <c r="I21" s="36" t="n"/>
+      <c r="J21" s="37">
         <f>IF(OR(I21="",$D21=""),"",I21*$D21)</f>
         <v/>
       </c>
-      <c r="K21" s="29" t="n"/>
-      <c r="L21" s="30">
+      <c r="K21" s="36" t="n"/>
+      <c r="L21" s="37">
         <f>IF(OR(K21="",$D21=""),"",K21*$D21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="n">
+      <c r="A22" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="28" t="n"/>
-      <c r="E22" s="29" t="n"/>
-      <c r="F22" s="30">
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="35" t="n"/>
+      <c r="E22" s="36" t="n"/>
+      <c r="F22" s="37">
         <f>IF(OR(E22="",$D22=""),"",E22*$D22)</f>
         <v/>
       </c>
-      <c r="G22" s="29" t="n"/>
-      <c r="H22" s="30">
+      <c r="G22" s="36" t="n"/>
+      <c r="H22" s="37">
         <f>IF(OR(G22="",$D22=""),"",G22*$D22)</f>
         <v/>
       </c>
-      <c r="I22" s="29" t="n"/>
-      <c r="J22" s="30">
+      <c r="I22" s="36" t="n"/>
+      <c r="J22" s="37">
         <f>IF(OR(I22="",$D22=""),"",I22*$D22)</f>
         <v/>
       </c>
-      <c r="K22" s="29" t="n"/>
-      <c r="L22" s="30">
+      <c r="K22" s="36" t="n"/>
+      <c r="L22" s="37">
         <f>IF(OR(K22="",$D22=""),"",K22*$D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="31" t="inlineStr">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="38" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="F23" s="32">
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="39">
         <f>SUM(F8:F22)</f>
         <v/>
       </c>
-      <c r="H23" s="32">
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="39">
         <f>SUM(H8:H22)</f>
         <v/>
       </c>
-      <c r="J23" s="32">
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="39">
         <f>SUM(J8:J22)</f>
         <v/>
       </c>
-      <c r="L23" s="32">
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="39">
         <f>SUM(L8:L22)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="31" t="inlineStr">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="38" t="inlineStr">
         <is>
           <t>IVA 16%</t>
         </is>
       </c>
-      <c r="F24" s="32">
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="39">
         <f>ROUND(F23*0.16,2)</f>
         <v/>
       </c>
-      <c r="H24" s="32">
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="39">
         <f>ROUND(H23*0.16,2)</f>
         <v/>
       </c>
-      <c r="J24" s="32">
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="39">
         <f>ROUND(J23*0.16,2)</f>
         <v/>
       </c>
-      <c r="L24" s="32">
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="39">
         <f>ROUND(L23*0.16,2)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="31" t="inlineStr">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="38" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F25" s="32">
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="39">
         <f>F23+F24</f>
         <v/>
       </c>
-      <c r="H25" s="32">
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="39">
         <f>H23+H24</f>
         <v/>
       </c>
-      <c r="J25" s="32">
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="39">
         <f>J23+J24</f>
         <v/>
       </c>
-      <c r="L25" s="32">
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="39">
         <f>L23+L24</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Condiciones de pago</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="n"/>
-      <c r="H26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
-      <c r="L26" s="9" t="n"/>
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>CONDICIONES DE PAGO</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="17" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="17" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="17" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Tiempo de entrega (días)</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
-      <c r="L27" s="9" t="n"/>
-    </row>
-    <row r="28"/>
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>TIEMPO DE ENTREGA (DÍAS)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="17" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="17" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="17" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+    </row>
     <row r="29">
-      <c r="B29" s="33" t="inlineStr">
-        <is>
-          <t>MEJOR OPCIÓN (menor total)</t>
-        </is>
-      </c>
-      <c r="E29" s="31">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="40" t="inlineStr">
+        <is>
+          <t>MEJOR OPCIÓN (MENOR TOTAL)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="38">
         <f>IF(MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25))=1E+99,"",IF(F25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),E6,IF(H25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),G6,IF(J25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),I6,IF(L25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),K6,"")))))</f>
         <v/>
       </c>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
+      <c r="L29" s="4" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="34" t="inlineStr">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="41" t="inlineStr">
         <is>
           <t>Nota: si un proveedor no cotiza todas las partidas, su total no es comparable.</t>
         </is>
       </c>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -1555,4 +2317,822 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="44" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>RESUMEN DE COTIZACIONES</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="23" t="inlineStr">
+        <is>
+          <t>INSERTE SU LOGO
+(clic derecho &gt; Insertar imagen)</t>
+        </is>
+      </c>
+      <c r="I1" s="42" t="n"/>
+      <c r="J1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Comparativo de totales por proveedor</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="n"/>
+      <c r="C2" s="26" t="n"/>
+      <c r="D2" s="26" t="n"/>
+      <c r="E2" s="26" t="n"/>
+      <c r="F2" s="26" t="n"/>
+      <c r="G2" s="26" t="n"/>
+      <c r="H2" s="27" t="n"/>
+      <c r="I2" s="43" t="n"/>
+      <c r="J2" s="28" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="44" t="inlineStr">
+        <is>
+          <t>MEJOR OPCIÓN</t>
+        </is>
+      </c>
+      <c r="C4" s="45" t="n"/>
+      <c r="D4" s="44" t="inlineStr">
+        <is>
+          <t>TOTAL MÁS BAJO</t>
+        </is>
+      </c>
+      <c r="E4" s="45" t="n"/>
+      <c r="F4" s="44" t="inlineStr">
+        <is>
+          <t>TOTAL MÁS ALTO</t>
+        </is>
+      </c>
+      <c r="G4" s="45" t="n"/>
+      <c r="H4" s="44" t="inlineStr">
+        <is>
+          <t>AHORRO POTENCIAL</t>
+        </is>
+      </c>
+      <c r="I4" s="45" t="n"/>
+      <c r="J4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="46">
+        <f>FORMATO!E29</f>
+        <v/>
+      </c>
+      <c r="C5" s="47" t="n"/>
+      <c r="D5" s="48">
+        <f>IFERROR(MIN(C26:C29),0)</f>
+        <v/>
+      </c>
+      <c r="E5" s="47" t="n"/>
+      <c r="F5" s="48">
+        <f>IFERROR(MAX(C26:C29),0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="47" t="n"/>
+      <c r="H5" s="48">
+        <f>F5-D5</f>
+        <v/>
+      </c>
+      <c r="I5" s="47" t="n"/>
+      <c r="J5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>TOTAL CON IVA</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="32">
+        <f>IF(FORMATO!E6="","PROVEEDOR A",FORMATO!E6)</f>
+        <v/>
+      </c>
+      <c r="C26" s="37">
+        <f>IF(FORMATO!F25=0,"",FORMATO!F25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="32">
+        <f>IF(FORMATO!G6="","PROVEEDOR B",FORMATO!G6)</f>
+        <v/>
+      </c>
+      <c r="C27" s="37">
+        <f>IF(FORMATO!H25=0,"",FORMATO!H25)</f>
+        <v/>
+      </c>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="32">
+        <f>IF(FORMATO!I6="","PROVEEDOR C",FORMATO!I6)</f>
+        <v/>
+      </c>
+      <c r="C28" s="37">
+        <f>IF(FORMATO!J25=0,"",FORMATO!J25)</f>
+        <v/>
+      </c>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="32">
+        <f>IF(FORMATO!K6="","PROVEEDOR D",FORMATO!K6)</f>
+        <v/>
+      </c>
+      <c r="C29" s="37">
+        <f>IF(FORMATO!L25=0,"",FORMATO!L25)</f>
+        <v/>
+      </c>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="11">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H1:J2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 Página &amp;P&amp;R&amp;8 Impreso: &amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001B6B73"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="49" t="inlineStr">
+        <is>
+          <t>AYUDA Y PREGUNTAS FRECUENTES</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="50" t="inlineStr">
+        <is>
+          <t>CUADRO COMPARATIVO</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>PREGUNTAS FRECUENTES</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="51" t="inlineStr">
+        <is>
+          <t>¿Cuántos proveedores puedo comparar?</t>
+        </is>
+      </c>
+      <c r="D6" s="52" t="inlineStr">
+        <is>
+          <t>Hasta cuatro.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="51" t="inlineStr">
+        <is>
+          <t>¿Cómo decido si el más barato no es el mejor?</t>
+        </is>
+      </c>
+      <c r="D7" s="52" t="inlineStr">
+        <is>
+          <t>Anota la justificación y adjunta la autorización del responsable.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="53" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="51" t="inlineStr">
+        <is>
+          <t>¿Por qué no puedo escribir en algunas celdas?</t>
+        </is>
+      </c>
+      <c r="D8" s="52" t="inlineStr">
+        <is>
+          <t>La hoja está protegida para que no se borren fórmulas por accidente. Solo se editan las celdas de captura (color crema). Si necesitas modificar algo más: pestaña Revisar &gt; Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="51" t="inlineStr">
+        <is>
+          <t>¿Cómo agrego mi logotipo?</t>
+        </is>
+      </c>
+      <c r="D9" s="52" t="inlineStr">
+        <is>
+          <t>Haz clic en el recuadro punteado de la esquina superior derecha del formato y usa Insertar &gt; Imágenes. Ajusta el tamaño sin salirte del recuadro.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="51" t="inlineStr">
+        <is>
+          <t>¿Cómo lo imprimo o lo convierto a PDF?</t>
+        </is>
+      </c>
+      <c r="D10" s="52" t="inlineStr">
+        <is>
+          <t>Archivo &gt; Imprimir (ya está ajustado a una hoja de ancho). Para PDF elige 'Microsoft Print to PDF' o Archivo &gt; Exportar &gt; PDF.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="51" t="inlineStr">
+        <is>
+          <t>¿Con qué versiones de Excel funciona?</t>
+        </is>
+      </c>
+      <c r="D11" s="52" t="inlineStr">
+        <is>
+          <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac). Funciona en LibreOffice y Google Sheets, aunque algunas gráficas y formatos pueden verse distintos.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="51" t="inlineStr">
+        <is>
+          <t>¿Por qué la letra se ve diferente?</t>
+        </is>
+      </c>
+      <c r="D12" s="52" t="inlineStr">
+        <is>
+          <t>El diseño usa la fuente Abadi, incluida en Microsoft 365. Si tu versión no la tiene, Excel la sustituye por otra; no afecta el funcionamiento.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="38" customHeight="1">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="51" t="inlineStr">
+        <is>
+          <t>¿Puedo usarlo en varias empresas o por varios años?</t>
+        </is>
+      </c>
+      <c r="D13" s="52" t="inlineStr">
+        <is>
+          <t>Sí. Guarda una copia del archivo por empresa o por periodo (Archivo &gt; Guardar como) y deja el original en blanco como plantilla maestra.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>GLOSARIO</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="53" t="inlineStr">
+        <is>
+          <t>COTIZACIÓN</t>
+        </is>
+      </c>
+      <c r="D16" s="54" t="inlineStr">
+        <is>
+          <t>Oferta formal de precio por parte de un proveedor.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="53" t="inlineStr">
+        <is>
+          <t>REQUISICIÓN</t>
+        </is>
+      </c>
+      <c r="D17" s="54" t="inlineStr">
+        <is>
+          <t>Solicitud interna de compra.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="53" t="inlineStr">
+        <is>
+          <t>CONDICIONES COMERCIALES</t>
+        </is>
+      </c>
+      <c r="D18" s="54" t="inlineStr">
+        <is>
+          <t>Crédito, garantía y entrega.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>LISTA DE VERIFICACIÓN (marca ☑ al completar)</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="55" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C21" s="56" t="inlineStr">
+        <is>
+          <t>Requisición autorizada</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="55" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C22" s="56" t="inlineStr">
+        <is>
+          <t>Cotizaciones recibidas con la misma especificación</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="55" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C23" s="56" t="inlineStr">
+        <is>
+          <t>Cuadro llenado y firmado</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="55" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C24" s="56" t="inlineStr">
+        <is>
+          <t>Proveedor seleccionado notificado</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="6">
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B21 B22 B23 B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"☐,☑"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/plantillas/3_Inventarios_y_Compras/04_Cuadro_Comparativo_de_Cotizaciones.xlsx
+++ b/plantillas/3_Inventarios_y_Compras/04_Cuadro_Comparativo_de_Cotizaciones.xlsx
@@ -53,7 +53,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
     </font>
     <font>
       <name val="Abadi"/>
@@ -72,7 +72,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="9"/>
     </font>
     <font>
@@ -114,7 +114,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="12"/>
     </font>
     <font>
@@ -137,7 +137,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="11"/>
     </font>
     <font>
@@ -165,7 +165,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -572,11 +572,11 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="1B6B73"/>
+              <a:srgbClr val="0E7C8B"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="1B6B73"/>
+                <a:srgbClr val="0E7C8B"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2795,7 +2795,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001B6B73"/>
+    <tabColor rgb="000E7C8B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/plantillas/3_Inventarios_y_Compras/04_Cuadro_Comparativo_de_Cotizaciones.xlsx
+++ b/plantillas/3_Inventarios_y_Compras/04_Cuadro_Comparativo_de_Cotizaciones.xlsx
@@ -969,7 +969,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE</t>
+          <t>FORMATOS ADMINISTRATIVOS</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -1451,7 +1451,7 @@
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE  ·  Formatos administrativos  ·  Para uso interno de tu empresa</t>
+          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
         </is>
       </c>
       <c r="C38" s="4" t="n"/>

--- a/plantillas/3_Inventarios_y_Compras/04_Cuadro_Comparativo_de_Cotizaciones.xlsx
+++ b/plantillas/3_Inventarios_y_Compras/04_Cuadro_Comparativo_de_Cotizaciones.xlsx
@@ -12,7 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMEN" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYUDA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'FORMATO'!$7:$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -24,7 +26,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.##"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,153 +35,160 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="20"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00A6A6A6"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="007F7F7F"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000B2A4A"/>
-      <sz val="18"/>
+      <sz val="24"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9D3DB"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="30"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00C9D3DB"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000E7C8B"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002B2B2B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000B2A4A"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
-      <color rgb="002B2B2B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="00C9D3DB"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="18"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="000B2A4A"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -202,6 +211,16 @@
       </patternFill>
     </fill>
     <fill>
+      <gradientFill type="linear" degree="90">
+        <stop position="0">
+          <color rgb="0017426B"/>
+        </stop>
+        <stop position="1">
+          <color rgb="000B2A4A"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF2F5"/>
       </patternFill>
@@ -212,7 +231,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -281,6 +300,20 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00C9D3DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
+    </border>
+    <border>
       <top style="dashed">
         <color rgb="00A6A6A6"/>
       </top>
@@ -343,6 +376,11 @@
     </border>
     <border>
       <bottom style="thin">
+        <color rgb="00E3E8ED"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
         <color rgb="00C9D3DB"/>
       </bottom>
     </border>
@@ -350,24 +388,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -378,19 +416,27 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -399,67 +445,76 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="26" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="27" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="27" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="27" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="9" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="9" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="27" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -542,6 +597,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
   <chart>
     <title>
       <tx>
@@ -572,11 +628,11 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="0E7C8B"/>
+              <a:srgbClr val="12A0A8"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="0E7C8B"/>
+                <a:srgbClr val="12A0A8"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -592,7 +648,7 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="70"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -615,6 +671,16 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E8ED"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -624,6 +690,12 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -944,7 +1016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1203,7 +1275,7 @@
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>CÓMO USARLO</t>
+          <t>FICHA TÉCNICA</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -1214,77 +1286,87 @@
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="4" t="n"/>
-      <c r="B21" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Renombra los proveedores en la fila 6.</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Capacidad</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>15 partidas · 4 proveedores</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
       <c r="G21" s="4" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="4" t="n"/>
-      <c r="B22" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Captura descripción, unidad y cantidad de cada partida y el precio unitario ofrecido por proveedor.</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Compatibilidad</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac)</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
       <c r="G22" s="4" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="4" t="n"/>
-      <c r="B23" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Importes, IVA y total se calculan; abajo se indica el proveedor con el menor total.</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Idioma y moneda</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>Español (México) · Pesos mexicanos (MXN) · IVA 16%</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
       <c r="G23" s="4" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="4" t="n"/>
-      <c r="B24" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Anota condiciones de pago y tiempos de entrega, pues el precio no es el único criterio.</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Protección</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>Hojas protegidas sin contraseña (Revisar &gt; Desproteger hoja)</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
       <c r="G24" s="4" t="n"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="21" customHeight="1">
       <c r="A25" s="4" t="n"/>
-      <c r="B25" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Arial (disponible en Windows, Mac y Google Sheets)</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
       <c r="G25" s="4" t="n"/>
     </row>
     <row r="26">
@@ -1300,7 +1382,7 @@
       <c r="A27" s="4" t="n"/>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>RECOMENDACIONES DE USO</t>
+          <t>CÓMO USARLO</t>
         </is>
       </c>
       <c r="C27" s="10" t="n"/>
@@ -1311,14 +1393,12 @@
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="4" t="n"/>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B28" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Solicita al menos tres cotizaciones con las mismas especificaciones.</t>
+          <t>Renombra los proveedores en la fila 6.</t>
         </is>
       </c>
       <c r="D28" s="4" t="n"/>
@@ -1328,14 +1408,12 @@
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="4" t="n"/>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B29" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>El precio no es el único criterio: valora calidad, garantía, tiempo de entrega y crédito.</t>
+          <t>Captura descripción, unidad y cantidad de cada partida y el precio unitario ofrecido por proveedor.</t>
         </is>
       </c>
       <c r="D29" s="4" t="n"/>
@@ -1345,14 +1423,12 @@
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="4" t="n"/>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B30" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>Si un proveedor no cotiza todas las partidas, no es comparable en el total.</t>
+          <t>Importes, IVA y total se calculan; abajo se indica el proveedor con el menor total.</t>
         </is>
       </c>
       <c r="D30" s="4" t="n"/>
@@ -1362,14 +1438,12 @@
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="4" t="n"/>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B31" s="18" t="n">
+        <v>4</v>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>Archiva el cuadro como soporte de la decisión de compra.</t>
+          <t>Anota condiciones de pago y tiempos de entrega, pues el precio no es el único criterio.</t>
         </is>
       </c>
       <c r="D31" s="4" t="n"/>
@@ -1377,47 +1451,53 @@
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" ht="36" customHeight="1">
       <c r="A32" s="4" t="n"/>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
+      <c r="B32" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
+        </is>
+      </c>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
     </row>
-    <row r="33" ht="24" customHeight="1">
+    <row r="33">
       <c r="A33" s="4" t="n"/>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>LEYENDA DE COLORES</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="10" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" ht="24" customHeight="1">
       <c r="A34" s="4" t="n"/>
-      <c r="B34" s="17" t="inlineStr"/>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>CELDA DE CAPTURA: escribe aquí.</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>RECOMENDACIONES DE USO</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
       <c r="G34" s="4" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="21" customHeight="1">
       <c r="A35" s="4" t="n"/>
-      <c r="B35" s="19" t="inlineStr"/>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Solicita al menos tres cotizaciones con las mismas especificaciones.</t>
         </is>
       </c>
       <c r="D35" s="4" t="n"/>
@@ -1425,12 +1505,16 @@
       <c r="F35" s="4" t="n"/>
       <c r="G35" s="4" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="21" customHeight="1">
       <c r="A36" s="4" t="n"/>
-      <c r="B36" s="20" t="inlineStr"/>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>ENCABEZADOS Y TÍTULOS.</t>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>El precio no es el único criterio: valora calidad, garantía, tiempo de entrega y crédito.</t>
         </is>
       </c>
       <c r="D36" s="4" t="n"/>
@@ -1438,48 +1522,166 @@
       <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" ht="21" customHeight="1">
       <c r="A37" s="4" t="n"/>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Si un proveedor no cotiza todas las partidas, no es comparable en el total.</t>
+        </is>
+      </c>
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
     </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="1" t="n"/>
-      <c r="B38" s="21" t="inlineStr">
-        <is>
-          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n"/>
+    <row r="38" ht="21" customHeight="1">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Archiva el cuadro como soporte de la decisión de compra.</t>
+        </is>
+      </c>
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
-      <c r="G38" s="1" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>LEYENDA DE COLORES</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="20" t="inlineStr"/>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>CELDA DE CAPTURA: escribe aquí.</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="22" t="inlineStr"/>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="23" t="inlineStr"/>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>ENCABEZADOS Y TÍTULOS.</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="24" t="inlineStr"/>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>* CAMPO OBLIGATORIO: complétalo antes de imprimir o enviar.</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="1" t="n"/>
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="1" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="16">
-    <mergeCell ref="C22:F22"/>
+  <mergeCells count="21">
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B4:F5"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C29:F29"/>
     <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C23:F23"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="B4:F5"/>
-    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="C36:F36"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId3"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
@@ -1511,7 +1713,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>CUADRO COMPARATIVO DE COTIZACIONES</t>
         </is>
@@ -1525,31 +1727,31 @@
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
-      <c r="K1" s="23" t="inlineStr">
+      <c r="K1" s="27" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="L1" s="24" t="n"/>
+      <c r="L1" s="28" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Compara hasta 4 proveedores y selecciona la mejor opción</t>
         </is>
       </c>
-      <c r="B2" s="26" t="n"/>
-      <c r="C2" s="26" t="n"/>
-      <c r="D2" s="26" t="n"/>
-      <c r="E2" s="26" t="n"/>
-      <c r="F2" s="26" t="n"/>
-      <c r="G2" s="26" t="n"/>
-      <c r="H2" s="26" t="n"/>
-      <c r="I2" s="26" t="n"/>
-      <c r="J2" s="26" t="n"/>
-      <c r="K2" s="27" t="n"/>
-      <c r="L2" s="28" t="n"/>
+      <c r="B2" s="30" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="30" t="n"/>
+      <c r="E2" s="30" t="n"/>
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30" t="n"/>
+      <c r="H2" s="30" t="n"/>
+      <c r="I2" s="30" t="n"/>
+      <c r="J2" s="30" t="n"/>
+      <c r="K2" s="31" t="n"/>
+      <c r="L2" s="32" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -1566,21 +1768,21 @@
       <c r="L3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>REQUISICIÓN NO.</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n"/>
-      <c r="C4" s="17" t="n"/>
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="20" t="n"/>
       <c r="D4" s="4" t="n"/>
-      <c r="E4" s="29" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="F4" s="30" t="n"/>
-      <c r="G4" s="17" t="n"/>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t>FECHA *</t>
+        </is>
+      </c>
+      <c r="F4" s="34" t="n"/>
+      <c r="G4" s="20" t="n"/>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
@@ -1606,516 +1808,516 @@
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>Proveedor A</t>
         </is>
       </c>
-      <c r="F6" s="32" t="n"/>
-      <c r="G6" s="31" t="inlineStr">
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t>Proveedor B</t>
         </is>
       </c>
-      <c r="H6" s="32" t="n"/>
-      <c r="I6" s="31" t="inlineStr">
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="35" t="inlineStr">
         <is>
           <t>Proveedor C</t>
         </is>
       </c>
-      <c r="J6" s="32" t="n"/>
-      <c r="K6" s="31" t="inlineStr">
+      <c r="J6" s="36" t="n"/>
+      <c r="K6" s="35" t="inlineStr">
         <is>
           <t>Proveedor D</t>
         </is>
       </c>
-      <c r="L6" s="32" t="n"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="L6" s="36" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>PART.</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>DESCRIPCIÓN</t>
         </is>
       </c>
-      <c r="C7" s="33" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D7" s="33" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>CANTIDAD</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>P. UNIT.</t>
         </is>
       </c>
-      <c r="F7" s="33" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>IMPORTE</t>
         </is>
       </c>
-      <c r="G7" s="33" t="inlineStr">
+      <c r="G7" s="37" t="inlineStr">
         <is>
           <t>P. UNIT.</t>
         </is>
       </c>
-      <c r="H7" s="33" t="inlineStr">
+      <c r="H7" s="37" t="inlineStr">
         <is>
           <t>IMPORTE</t>
         </is>
       </c>
-      <c r="I7" s="33" t="inlineStr">
+      <c r="I7" s="37" t="inlineStr">
         <is>
           <t>P. UNIT.</t>
         </is>
       </c>
-      <c r="J7" s="33" t="inlineStr">
+      <c r="J7" s="37" t="inlineStr">
         <is>
           <t>IMPORTE</t>
         </is>
       </c>
-      <c r="K7" s="33" t="inlineStr">
+      <c r="K7" s="37" t="inlineStr">
         <is>
           <t>P. UNIT.</t>
         </is>
       </c>
-      <c r="L7" s="33" t="inlineStr">
+      <c r="L7" s="37" t="inlineStr">
         <is>
           <t>IMPORTE</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="34" t="n">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="17" t="n"/>
-      <c r="C8" s="17" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="37">
+      <c r="B8" s="39" t="n"/>
+      <c r="C8" s="39" t="n"/>
+      <c r="D8" s="40" t="n"/>
+      <c r="E8" s="41" t="n"/>
+      <c r="F8" s="42">
         <f>IF(OR(E8="",$D8=""),"",E8*$D8)</f>
         <v/>
       </c>
-      <c r="G8" s="36" t="n"/>
-      <c r="H8" s="37">
+      <c r="G8" s="41" t="n"/>
+      <c r="H8" s="42">
         <f>IF(OR(G8="",$D8=""),"",G8*$D8)</f>
         <v/>
       </c>
-      <c r="I8" s="36" t="n"/>
-      <c r="J8" s="37">
+      <c r="I8" s="41" t="n"/>
+      <c r="J8" s="42">
         <f>IF(OR(I8="",$D8=""),"",I8*$D8)</f>
         <v/>
       </c>
-      <c r="K8" s="36" t="n"/>
-      <c r="L8" s="37">
+      <c r="K8" s="41" t="n"/>
+      <c r="L8" s="42">
         <f>IF(OR(K8="",$D8=""),"",K8*$D8)</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="34" t="n">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="36" t="n"/>
-      <c r="F9" s="37">
+      <c r="B9" s="39" t="n"/>
+      <c r="C9" s="39" t="n"/>
+      <c r="D9" s="40" t="n"/>
+      <c r="E9" s="41" t="n"/>
+      <c r="F9" s="42">
         <f>IF(OR(E9="",$D9=""),"",E9*$D9)</f>
         <v/>
       </c>
-      <c r="G9" s="36" t="n"/>
-      <c r="H9" s="37">
+      <c r="G9" s="41" t="n"/>
+      <c r="H9" s="42">
         <f>IF(OR(G9="",$D9=""),"",G9*$D9)</f>
         <v/>
       </c>
-      <c r="I9" s="36" t="n"/>
-      <c r="J9" s="37">
+      <c r="I9" s="41" t="n"/>
+      <c r="J9" s="42">
         <f>IF(OR(I9="",$D9=""),"",I9*$D9)</f>
         <v/>
       </c>
-      <c r="K9" s="36" t="n"/>
-      <c r="L9" s="37">
+      <c r="K9" s="41" t="n"/>
+      <c r="L9" s="42">
         <f>IF(OR(K9="",$D9=""),"",K9*$D9)</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="34" t="n">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="17" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="37">
+      <c r="B10" s="39" t="n"/>
+      <c r="C10" s="39" t="n"/>
+      <c r="D10" s="40" t="n"/>
+      <c r="E10" s="41" t="n"/>
+      <c r="F10" s="42">
         <f>IF(OR(E10="",$D10=""),"",E10*$D10)</f>
         <v/>
       </c>
-      <c r="G10" s="36" t="n"/>
-      <c r="H10" s="37">
+      <c r="G10" s="41" t="n"/>
+      <c r="H10" s="42">
         <f>IF(OR(G10="",$D10=""),"",G10*$D10)</f>
         <v/>
       </c>
-      <c r="I10" s="36" t="n"/>
-      <c r="J10" s="37">
+      <c r="I10" s="41" t="n"/>
+      <c r="J10" s="42">
         <f>IF(OR(I10="",$D10=""),"",I10*$D10)</f>
         <v/>
       </c>
-      <c r="K10" s="36" t="n"/>
-      <c r="L10" s="37">
+      <c r="K10" s="41" t="n"/>
+      <c r="L10" s="42">
         <f>IF(OR(K10="",$D10=""),"",K10*$D10)</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="34" t="n">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="37">
+      <c r="B11" s="39" t="n"/>
+      <c r="C11" s="39" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="41" t="n"/>
+      <c r="F11" s="42">
         <f>IF(OR(E11="",$D11=""),"",E11*$D11)</f>
         <v/>
       </c>
-      <c r="G11" s="36" t="n"/>
-      <c r="H11" s="37">
+      <c r="G11" s="41" t="n"/>
+      <c r="H11" s="42">
         <f>IF(OR(G11="",$D11=""),"",G11*$D11)</f>
         <v/>
       </c>
-      <c r="I11" s="36" t="n"/>
-      <c r="J11" s="37">
+      <c r="I11" s="41" t="n"/>
+      <c r="J11" s="42">
         <f>IF(OR(I11="",$D11=""),"",I11*$D11)</f>
         <v/>
       </c>
-      <c r="K11" s="36" t="n"/>
-      <c r="L11" s="37">
+      <c r="K11" s="41" t="n"/>
+      <c r="L11" s="42">
         <f>IF(OR(K11="",$D11=""),"",K11*$D11)</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="34" t="n">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="37">
+      <c r="B12" s="39" t="n"/>
+      <c r="C12" s="39" t="n"/>
+      <c r="D12" s="40" t="n"/>
+      <c r="E12" s="41" t="n"/>
+      <c r="F12" s="42">
         <f>IF(OR(E12="",$D12=""),"",E12*$D12)</f>
         <v/>
       </c>
-      <c r="G12" s="36" t="n"/>
-      <c r="H12" s="37">
+      <c r="G12" s="41" t="n"/>
+      <c r="H12" s="42">
         <f>IF(OR(G12="",$D12=""),"",G12*$D12)</f>
         <v/>
       </c>
-      <c r="I12" s="36" t="n"/>
-      <c r="J12" s="37">
+      <c r="I12" s="41" t="n"/>
+      <c r="J12" s="42">
         <f>IF(OR(I12="",$D12=""),"",I12*$D12)</f>
         <v/>
       </c>
-      <c r="K12" s="36" t="n"/>
-      <c r="L12" s="37">
+      <c r="K12" s="41" t="n"/>
+      <c r="L12" s="42">
         <f>IF(OR(K12="",$D12=""),"",K12*$D12)</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="34" t="n">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="17" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="37">
+      <c r="B13" s="39" t="n"/>
+      <c r="C13" s="39" t="n"/>
+      <c r="D13" s="40" t="n"/>
+      <c r="E13" s="41" t="n"/>
+      <c r="F13" s="42">
         <f>IF(OR(E13="",$D13=""),"",E13*$D13)</f>
         <v/>
       </c>
-      <c r="G13" s="36" t="n"/>
-      <c r="H13" s="37">
+      <c r="G13" s="41" t="n"/>
+      <c r="H13" s="42">
         <f>IF(OR(G13="",$D13=""),"",G13*$D13)</f>
         <v/>
       </c>
-      <c r="I13" s="36" t="n"/>
-      <c r="J13" s="37">
+      <c r="I13" s="41" t="n"/>
+      <c r="J13" s="42">
         <f>IF(OR(I13="",$D13=""),"",I13*$D13)</f>
         <v/>
       </c>
-      <c r="K13" s="36" t="n"/>
-      <c r="L13" s="37">
+      <c r="K13" s="41" t="n"/>
+      <c r="L13" s="42">
         <f>IF(OR(K13="",$D13=""),"",K13*$D13)</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="34" t="n">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="38" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="37">
+      <c r="B14" s="39" t="n"/>
+      <c r="C14" s="39" t="n"/>
+      <c r="D14" s="40" t="n"/>
+      <c r="E14" s="41" t="n"/>
+      <c r="F14" s="42">
         <f>IF(OR(E14="",$D14=""),"",E14*$D14)</f>
         <v/>
       </c>
-      <c r="G14" s="36" t="n"/>
-      <c r="H14" s="37">
+      <c r="G14" s="41" t="n"/>
+      <c r="H14" s="42">
         <f>IF(OR(G14="",$D14=""),"",G14*$D14)</f>
         <v/>
       </c>
-      <c r="I14" s="36" t="n"/>
-      <c r="J14" s="37">
+      <c r="I14" s="41" t="n"/>
+      <c r="J14" s="42">
         <f>IF(OR(I14="",$D14=""),"",I14*$D14)</f>
         <v/>
       </c>
-      <c r="K14" s="36" t="n"/>
-      <c r="L14" s="37">
+      <c r="K14" s="41" t="n"/>
+      <c r="L14" s="42">
         <f>IF(OR(K14="",$D14=""),"",K14*$D14)</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="34" t="n">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="38" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="37">
+      <c r="B15" s="39" t="n"/>
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="40" t="n"/>
+      <c r="E15" s="41" t="n"/>
+      <c r="F15" s="42">
         <f>IF(OR(E15="",$D15=""),"",E15*$D15)</f>
         <v/>
       </c>
-      <c r="G15" s="36" t="n"/>
-      <c r="H15" s="37">
+      <c r="G15" s="41" t="n"/>
+      <c r="H15" s="42">
         <f>IF(OR(G15="",$D15=""),"",G15*$D15)</f>
         <v/>
       </c>
-      <c r="I15" s="36" t="n"/>
-      <c r="J15" s="37">
+      <c r="I15" s="41" t="n"/>
+      <c r="J15" s="42">
         <f>IF(OR(I15="",$D15=""),"",I15*$D15)</f>
         <v/>
       </c>
-      <c r="K15" s="36" t="n"/>
-      <c r="L15" s="37">
+      <c r="K15" s="41" t="n"/>
+      <c r="L15" s="42">
         <f>IF(OR(K15="",$D15=""),"",K15*$D15)</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="34" t="n">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="38" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="17" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="37">
+      <c r="B16" s="39" t="n"/>
+      <c r="C16" s="39" t="n"/>
+      <c r="D16" s="40" t="n"/>
+      <c r="E16" s="41" t="n"/>
+      <c r="F16" s="42">
         <f>IF(OR(E16="",$D16=""),"",E16*$D16)</f>
         <v/>
       </c>
-      <c r="G16" s="36" t="n"/>
-      <c r="H16" s="37">
+      <c r="G16" s="41" t="n"/>
+      <c r="H16" s="42">
         <f>IF(OR(G16="",$D16=""),"",G16*$D16)</f>
         <v/>
       </c>
-      <c r="I16" s="36" t="n"/>
-      <c r="J16" s="37">
+      <c r="I16" s="41" t="n"/>
+      <c r="J16" s="42">
         <f>IF(OR(I16="",$D16=""),"",I16*$D16)</f>
         <v/>
       </c>
-      <c r="K16" s="36" t="n"/>
-      <c r="L16" s="37">
+      <c r="K16" s="41" t="n"/>
+      <c r="L16" s="42">
         <f>IF(OR(K16="",$D16=""),"",K16*$D16)</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="34" t="n">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="38" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="17" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="37">
+      <c r="B17" s="39" t="n"/>
+      <c r="C17" s="39" t="n"/>
+      <c r="D17" s="40" t="n"/>
+      <c r="E17" s="41" t="n"/>
+      <c r="F17" s="42">
         <f>IF(OR(E17="",$D17=""),"",E17*$D17)</f>
         <v/>
       </c>
-      <c r="G17" s="36" t="n"/>
-      <c r="H17" s="37">
+      <c r="G17" s="41" t="n"/>
+      <c r="H17" s="42">
         <f>IF(OR(G17="",$D17=""),"",G17*$D17)</f>
         <v/>
       </c>
-      <c r="I17" s="36" t="n"/>
-      <c r="J17" s="37">
+      <c r="I17" s="41" t="n"/>
+      <c r="J17" s="42">
         <f>IF(OR(I17="",$D17=""),"",I17*$D17)</f>
         <v/>
       </c>
-      <c r="K17" s="36" t="n"/>
-      <c r="L17" s="37">
+      <c r="K17" s="41" t="n"/>
+      <c r="L17" s="42">
         <f>IF(OR(K17="",$D17=""),"",K17*$D17)</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="34" t="n">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="38" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="37">
+      <c r="B18" s="39" t="n"/>
+      <c r="C18" s="39" t="n"/>
+      <c r="D18" s="40" t="n"/>
+      <c r="E18" s="41" t="n"/>
+      <c r="F18" s="42">
         <f>IF(OR(E18="",$D18=""),"",E18*$D18)</f>
         <v/>
       </c>
-      <c r="G18" s="36" t="n"/>
-      <c r="H18" s="37">
+      <c r="G18" s="41" t="n"/>
+      <c r="H18" s="42">
         <f>IF(OR(G18="",$D18=""),"",G18*$D18)</f>
         <v/>
       </c>
-      <c r="I18" s="36" t="n"/>
-      <c r="J18" s="37">
+      <c r="I18" s="41" t="n"/>
+      <c r="J18" s="42">
         <f>IF(OR(I18="",$D18=""),"",I18*$D18)</f>
         <v/>
       </c>
-      <c r="K18" s="36" t="n"/>
-      <c r="L18" s="37">
+      <c r="K18" s="41" t="n"/>
+      <c r="L18" s="42">
         <f>IF(OR(K18="",$D18=""),"",K18*$D18)</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="34" t="n">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="38" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="37">
+      <c r="B19" s="39" t="n"/>
+      <c r="C19" s="39" t="n"/>
+      <c r="D19" s="40" t="n"/>
+      <c r="E19" s="41" t="n"/>
+      <c r="F19" s="42">
         <f>IF(OR(E19="",$D19=""),"",E19*$D19)</f>
         <v/>
       </c>
-      <c r="G19" s="36" t="n"/>
-      <c r="H19" s="37">
+      <c r="G19" s="41" t="n"/>
+      <c r="H19" s="42">
         <f>IF(OR(G19="",$D19=""),"",G19*$D19)</f>
         <v/>
       </c>
-      <c r="I19" s="36" t="n"/>
-      <c r="J19" s="37">
+      <c r="I19" s="41" t="n"/>
+      <c r="J19" s="42">
         <f>IF(OR(I19="",$D19=""),"",I19*$D19)</f>
         <v/>
       </c>
-      <c r="K19" s="36" t="n"/>
-      <c r="L19" s="37">
+      <c r="K19" s="41" t="n"/>
+      <c r="L19" s="42">
         <f>IF(OR(K19="",$D19=""),"",K19*$D19)</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="34" t="n">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="38" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="35" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="37">
+      <c r="B20" s="39" t="n"/>
+      <c r="C20" s="39" t="n"/>
+      <c r="D20" s="40" t="n"/>
+      <c r="E20" s="41" t="n"/>
+      <c r="F20" s="42">
         <f>IF(OR(E20="",$D20=""),"",E20*$D20)</f>
         <v/>
       </c>
-      <c r="G20" s="36" t="n"/>
-      <c r="H20" s="37">
+      <c r="G20" s="41" t="n"/>
+      <c r="H20" s="42">
         <f>IF(OR(G20="",$D20=""),"",G20*$D20)</f>
         <v/>
       </c>
-      <c r="I20" s="36" t="n"/>
-      <c r="J20" s="37">
+      <c r="I20" s="41" t="n"/>
+      <c r="J20" s="42">
         <f>IF(OR(I20="",$D20=""),"",I20*$D20)</f>
         <v/>
       </c>
-      <c r="K20" s="36" t="n"/>
-      <c r="L20" s="37">
+      <c r="K20" s="41" t="n"/>
+      <c r="L20" s="42">
         <f>IF(OR(K20="",$D20=""),"",K20*$D20)</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="34" t="n">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="38" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="37">
+      <c r="B21" s="39" t="n"/>
+      <c r="C21" s="39" t="n"/>
+      <c r="D21" s="40" t="n"/>
+      <c r="E21" s="41" t="n"/>
+      <c r="F21" s="42">
         <f>IF(OR(E21="",$D21=""),"",E21*$D21)</f>
         <v/>
       </c>
-      <c r="G21" s="36" t="n"/>
-      <c r="H21" s="37">
+      <c r="G21" s="41" t="n"/>
+      <c r="H21" s="42">
         <f>IF(OR(G21="",$D21=""),"",G21*$D21)</f>
         <v/>
       </c>
-      <c r="I21" s="36" t="n"/>
-      <c r="J21" s="37">
+      <c r="I21" s="41" t="n"/>
+      <c r="J21" s="42">
         <f>IF(OR(I21="",$D21=""),"",I21*$D21)</f>
         <v/>
       </c>
-      <c r="K21" s="36" t="n"/>
-      <c r="L21" s="37">
+      <c r="K21" s="41" t="n"/>
+      <c r="L21" s="42">
         <f>IF(OR(K21="",$D21=""),"",K21*$D21)</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="34" t="n">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="38" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="35" t="n"/>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="37">
+      <c r="B22" s="39" t="n"/>
+      <c r="C22" s="39" t="n"/>
+      <c r="D22" s="40" t="n"/>
+      <c r="E22" s="41" t="n"/>
+      <c r="F22" s="42">
         <f>IF(OR(E22="",$D22=""),"",E22*$D22)</f>
         <v/>
       </c>
-      <c r="G22" s="36" t="n"/>
-      <c r="H22" s="37">
+      <c r="G22" s="41" t="n"/>
+      <c r="H22" s="42">
         <f>IF(OR(G22="",$D22=""),"",G22*$D22)</f>
         <v/>
       </c>
-      <c r="I22" s="36" t="n"/>
-      <c r="J22" s="37">
+      <c r="I22" s="41" t="n"/>
+      <c r="J22" s="42">
         <f>IF(OR(I22="",$D22=""),"",I22*$D22)</f>
         <v/>
       </c>
-      <c r="K22" s="36" t="n"/>
-      <c r="L22" s="37">
+      <c r="K22" s="41" t="n"/>
+      <c r="L22" s="42">
         <f>IF(OR(K22="",$D22=""),"",K22*$D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n"/>
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B23" s="43" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
@@ -2123,29 +2325,29 @@
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
-      <c r="F23" s="39">
+      <c r="F23" s="44">
         <f>SUM(F8:F22)</f>
         <v/>
       </c>
       <c r="G23" s="4" t="n"/>
-      <c r="H23" s="39">
+      <c r="H23" s="44">
         <f>SUM(H8:H22)</f>
         <v/>
       </c>
       <c r="I23" s="4" t="n"/>
-      <c r="J23" s="39">
+      <c r="J23" s="44">
         <f>SUM(J8:J22)</f>
         <v/>
       </c>
       <c r="K23" s="4" t="n"/>
-      <c r="L23" s="39">
+      <c r="L23" s="44">
         <f>SUM(L8:L22)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n"/>
-      <c r="B24" s="38" t="inlineStr">
+      <c r="B24" s="43" t="inlineStr">
         <is>
           <t>IVA 16%</t>
         </is>
@@ -2153,29 +2355,29 @@
       <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
-      <c r="F24" s="39">
+      <c r="F24" s="44">
         <f>ROUND(F23*0.16,2)</f>
         <v/>
       </c>
       <c r="G24" s="4" t="n"/>
-      <c r="H24" s="39">
+      <c r="H24" s="44">
         <f>ROUND(H23*0.16,2)</f>
         <v/>
       </c>
       <c r="I24" s="4" t="n"/>
-      <c r="J24" s="39">
+      <c r="J24" s="44">
         <f>ROUND(J23*0.16,2)</f>
         <v/>
       </c>
       <c r="K24" s="4" t="n"/>
-      <c r="L24" s="39">
+      <c r="L24" s="44">
         <f>ROUND(L23*0.16,2)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n"/>
-      <c r="B25" s="38" t="inlineStr">
+      <c r="B25" s="43" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -2183,22 +2385,22 @@
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="n"/>
-      <c r="F25" s="39">
+      <c r="F25" s="44">
         <f>F23+F24</f>
         <v/>
       </c>
       <c r="G25" s="4" t="n"/>
-      <c r="H25" s="39">
+      <c r="H25" s="44">
         <f>H23+H24</f>
         <v/>
       </c>
       <c r="I25" s="4" t="n"/>
-      <c r="J25" s="39">
+      <c r="J25" s="44">
         <f>J23+J24</f>
         <v/>
       </c>
       <c r="K25" s="4" t="n"/>
-      <c r="L25" s="39">
+      <c r="L25" s="44">
         <f>L23+L24</f>
         <v/>
       </c>
@@ -2213,13 +2415,13 @@
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
-      <c r="F26" s="17" t="n"/>
+      <c r="F26" s="20" t="n"/>
       <c r="G26" s="4" t="n"/>
-      <c r="H26" s="17" t="n"/>
+      <c r="H26" s="20" t="n"/>
       <c r="I26" s="4" t="n"/>
-      <c r="J26" s="17" t="n"/>
+      <c r="J26" s="20" t="n"/>
       <c r="K26" s="4" t="n"/>
-      <c r="L26" s="17" t="n"/>
+      <c r="L26" s="20" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n"/>
@@ -2231,13 +2433,13 @@
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
-      <c r="F27" s="17" t="n"/>
+      <c r="F27" s="20" t="n"/>
       <c r="G27" s="4" t="n"/>
-      <c r="H27" s="17" t="n"/>
+      <c r="H27" s="20" t="n"/>
       <c r="I27" s="4" t="n"/>
-      <c r="J27" s="17" t="n"/>
+      <c r="J27" s="20" t="n"/>
       <c r="K27" s="4" t="n"/>
-      <c r="L27" s="17" t="n"/>
+      <c r="L27" s="20" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n"/>
@@ -2255,14 +2457,14 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n"/>
-      <c r="B29" s="40" t="inlineStr">
+      <c r="B29" s="45" t="inlineStr">
         <is>
           <t>MEJOR OPCIÓN (MENOR TOTAL)</t>
         </is>
       </c>
       <c r="C29" s="4" t="n"/>
       <c r="D29" s="4" t="n"/>
-      <c r="E29" s="38">
+      <c r="E29" s="43">
         <f>IF(MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25))=1E+99,"",IF(F25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),E6,IF(H25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),G6,IF(J25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),I6,IF(L25=MIN(IF(F25=0,1E+99,F25),IF(H25=0,1E+99,H25),IF(J25=0,1E+99,J25),IF(L25=0,1E+99,L25)),K6,"")))))</f>
         <v/>
       </c>
@@ -2276,7 +2478,7 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n"/>
-      <c r="B30" s="41" t="inlineStr">
+      <c r="B30" s="46" t="inlineStr">
         <is>
           <t>Nota: si un proveedor no cotiza todas las partidas, su total no es comparable.</t>
         </is>
@@ -2305,6 +2507,20 @@
     <mergeCell ref="K6:L6"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
+  <dataValidations count="4">
+    <dataValidation sqref="E8:E22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G8:G22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I8:I22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K8:K22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1"/>
@@ -2342,7 +2558,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>RESUMEN DE COTIZACIONES</t>
         </is>
@@ -2353,30 +2569,30 @@
       <c r="E1" s="1" t="n"/>
       <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n"/>
-      <c r="H1" s="23" t="inlineStr">
+      <c r="H1" s="27" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="I1" s="42" t="n"/>
-      <c r="J1" s="24" t="n"/>
+      <c r="I1" s="47" t="n"/>
+      <c r="J1" s="28" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Comparativo de totales por proveedor</t>
         </is>
       </c>
-      <c r="B2" s="26" t="n"/>
-      <c r="C2" s="26" t="n"/>
-      <c r="D2" s="26" t="n"/>
-      <c r="E2" s="26" t="n"/>
-      <c r="F2" s="26" t="n"/>
-      <c r="G2" s="26" t="n"/>
-      <c r="H2" s="27" t="n"/>
-      <c r="I2" s="43" t="n"/>
-      <c r="J2" s="28" t="n"/>
+      <c r="B2" s="30" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="30" t="n"/>
+      <c r="E2" s="30" t="n"/>
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30" t="n"/>
+      <c r="H2" s="31" t="n"/>
+      <c r="I2" s="48" t="n"/>
+      <c r="J2" s="32" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -2390,56 +2606,56 @@
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="n"/>
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>MEJOR OPCIÓN</t>
         </is>
       </c>
-      <c r="C4" s="45" t="n"/>
-      <c r="D4" s="44" t="inlineStr">
+      <c r="C4" s="50" t="n"/>
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>TOTAL MÁS BAJO</t>
         </is>
       </c>
-      <c r="E4" s="45" t="n"/>
-      <c r="F4" s="44" t="inlineStr">
+      <c r="E4" s="50" t="n"/>
+      <c r="F4" s="49" t="inlineStr">
         <is>
           <t>TOTAL MÁS ALTO</t>
         </is>
       </c>
-      <c r="G4" s="45" t="n"/>
-      <c r="H4" s="44" t="inlineStr">
+      <c r="G4" s="50" t="n"/>
+      <c r="H4" s="49" t="inlineStr">
         <is>
           <t>AHORRO POTENCIAL</t>
         </is>
       </c>
-      <c r="I4" s="45" t="n"/>
+      <c r="I4" s="50" t="n"/>
       <c r="J4" s="4" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="46" customHeight="1">
       <c r="A5" s="4" t="n"/>
-      <c r="B5" s="46">
+      <c r="B5" s="51">
         <f>FORMATO!E29</f>
         <v/>
       </c>
-      <c r="C5" s="47" t="n"/>
-      <c r="D5" s="48">
+      <c r="C5" s="52" t="n"/>
+      <c r="D5" s="53">
         <f>IFERROR(MIN(C26:C29),0)</f>
         <v/>
       </c>
-      <c r="E5" s="47" t="n"/>
-      <c r="F5" s="48">
+      <c r="E5" s="52" t="n"/>
+      <c r="F5" s="53">
         <f>IFERROR(MAX(C26:C29),0)</f>
         <v/>
       </c>
-      <c r="G5" s="47" t="n"/>
-      <c r="H5" s="48">
+      <c r="G5" s="52" t="n"/>
+      <c r="H5" s="53">
         <f>F5-D5</f>
         <v/>
       </c>
-      <c r="I5" s="47" t="n"/>
+      <c r="I5" s="52" t="n"/>
       <c r="J5" s="4" t="n"/>
     </row>
     <row r="6">
@@ -2672,12 +2888,12 @@
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="4" t="n"/>
-      <c r="B25" s="33" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>PROVEEDOR</t>
         </is>
       </c>
-      <c r="C25" s="33" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>TOTAL CON IVA</t>
         </is>
@@ -2692,11 +2908,11 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n"/>
-      <c r="B26" s="32">
+      <c r="B26" s="36">
         <f>IF(FORMATO!E6="","PROVEEDOR A",FORMATO!E6)</f>
         <v/>
       </c>
-      <c r="C26" s="37">
+      <c r="C26" s="54">
         <f>IF(FORMATO!F25=0,"",FORMATO!F25)</f>
         <v/>
       </c>
@@ -2710,11 +2926,11 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n"/>
-      <c r="B27" s="32">
+      <c r="B27" s="36">
         <f>IF(FORMATO!G6="","PROVEEDOR B",FORMATO!G6)</f>
         <v/>
       </c>
-      <c r="C27" s="37">
+      <c r="C27" s="54">
         <f>IF(FORMATO!H25=0,"",FORMATO!H25)</f>
         <v/>
       </c>
@@ -2728,11 +2944,11 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n"/>
-      <c r="B28" s="32">
+      <c r="B28" s="36">
         <f>IF(FORMATO!I6="","PROVEEDOR C",FORMATO!I6)</f>
         <v/>
       </c>
-      <c r="C28" s="37">
+      <c r="C28" s="54">
         <f>IF(FORMATO!J25=0,"",FORMATO!J25)</f>
         <v/>
       </c>
@@ -2746,11 +2962,11 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n"/>
-      <c r="B29" s="32">
+      <c r="B29" s="36">
         <f>IF(FORMATO!K6="","PROVEEDOR D",FORMATO!K6)</f>
         <v/>
       </c>
-      <c r="C29" s="37">
+      <c r="C29" s="54">
         <f>IF(FORMATO!L25=0,"",FORMATO!L25)</f>
         <v/>
       </c>
@@ -2811,7 +3027,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="55" t="inlineStr">
         <is>
           <t>AYUDA Y PREGUNTAS FRECUENTES</t>
         </is>
@@ -2822,7 +3038,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n"/>
-      <c r="B2" s="50" t="inlineStr">
+      <c r="B2" s="56" t="inlineStr">
         <is>
           <t>CUADRO COMPARATIVO</t>
         </is>
@@ -2859,12 +3075,12 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="51" t="inlineStr">
+      <c r="C6" s="57" t="inlineStr">
         <is>
           <t>¿Cuántos proveedores puedo comparar?</t>
         </is>
       </c>
-      <c r="D6" s="52" t="inlineStr">
+      <c r="D6" s="58" t="inlineStr">
         <is>
           <t>Hasta cuatro.</t>
         </is>
@@ -2874,12 +3090,12 @@
     <row r="7" ht="38" customHeight="1">
       <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="n"/>
-      <c r="C7" s="51" t="inlineStr">
+      <c r="C7" s="57" t="inlineStr">
         <is>
           <t>¿Cómo decido si el más barato no es el mejor?</t>
         </is>
       </c>
-      <c r="D7" s="52" t="inlineStr">
+      <c r="D7" s="58" t="inlineStr">
         <is>
           <t>Anota la justificación y adjunta la autorización del responsable.</t>
         </is>
@@ -2889,12 +3105,12 @@
     <row r="8" ht="53" customHeight="1">
       <c r="A8" s="4" t="n"/>
       <c r="B8" s="4" t="n"/>
-      <c r="C8" s="51" t="inlineStr">
+      <c r="C8" s="57" t="inlineStr">
         <is>
           <t>¿Por qué no puedo escribir en algunas celdas?</t>
         </is>
       </c>
-      <c r="D8" s="52" t="inlineStr">
+      <c r="D8" s="58" t="inlineStr">
         <is>
           <t>La hoja está protegida para que no se borren fórmulas por accidente. Solo se editan las celdas de captura (color crema). Si necesitas modificar algo más: pestaña Revisar &gt; Desproteger hoja (no tiene contraseña).</t>
         </is>
@@ -2904,12 +3120,12 @@
     <row r="9" ht="38" customHeight="1">
       <c r="A9" s="4" t="n"/>
       <c r="B9" s="4" t="n"/>
-      <c r="C9" s="51" t="inlineStr">
+      <c r="C9" s="57" t="inlineStr">
         <is>
           <t>¿Cómo agrego mi logotipo?</t>
         </is>
       </c>
-      <c r="D9" s="52" t="inlineStr">
+      <c r="D9" s="58" t="inlineStr">
         <is>
           <t>Haz clic en el recuadro punteado de la esquina superior derecha del formato y usa Insertar &gt; Imágenes. Ajusta el tamaño sin salirte del recuadro.</t>
         </is>
@@ -2919,12 +3135,12 @@
     <row r="10" ht="38" customHeight="1">
       <c r="A10" s="4" t="n"/>
       <c r="B10" s="4" t="n"/>
-      <c r="C10" s="51" t="inlineStr">
+      <c r="C10" s="57" t="inlineStr">
         <is>
           <t>¿Cómo lo imprimo o lo convierto a PDF?</t>
         </is>
       </c>
-      <c r="D10" s="52" t="inlineStr">
+      <c r="D10" s="58" t="inlineStr">
         <is>
           <t>Archivo &gt; Imprimir (ya está ajustado a una hoja de ancho). Para PDF elige 'Microsoft Print to PDF' o Archivo &gt; Exportar &gt; PDF.</t>
         </is>
@@ -2934,12 +3150,12 @@
     <row r="11" ht="38" customHeight="1">
       <c r="A11" s="4" t="n"/>
       <c r="B11" s="4" t="n"/>
-      <c r="C11" s="51" t="inlineStr">
+      <c r="C11" s="57" t="inlineStr">
         <is>
           <t>¿Con qué versiones de Excel funciona?</t>
         </is>
       </c>
-      <c r="D11" s="52" t="inlineStr">
+      <c r="D11" s="58" t="inlineStr">
         <is>
           <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac). Funciona en LibreOffice y Google Sheets, aunque algunas gráficas y formatos pueden verse distintos.</t>
         </is>
@@ -2949,14 +3165,14 @@
     <row r="12" ht="38" customHeight="1">
       <c r="A12" s="4" t="n"/>
       <c r="B12" s="4" t="n"/>
-      <c r="C12" s="51" t="inlineStr">
-        <is>
-          <t>¿Por qué la letra se ve diferente?</t>
-        </is>
-      </c>
-      <c r="D12" s="52" t="inlineStr">
-        <is>
-          <t>El diseño usa la fuente Abadi, incluida en Microsoft 365. Si tu versión no la tiene, Excel la sustituye por otra; no afecta el funcionamiento.</t>
+      <c r="C12" s="57" t="inlineStr">
+        <is>
+          <t>¿Puedo cambiar la letra?</t>
+        </is>
+      </c>
+      <c r="D12" s="58" t="inlineStr">
+        <is>
+          <t>El diseño usa la fuente Arial, disponible en Windows, Mac y Google Sheets. Si necesitas otra, selecciona todo (Ctrl+E) y cambia la fuente; no afecta el funcionamiento.</t>
         </is>
       </c>
       <c r="E12" s="4" t="n"/>
@@ -2964,12 +3180,12 @@
     <row r="13" ht="38" customHeight="1">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="4" t="n"/>
-      <c r="C13" s="51" t="inlineStr">
+      <c r="C13" s="57" t="inlineStr">
         <is>
           <t>¿Puedo usarlo en varias empresas o por varios años?</t>
         </is>
       </c>
-      <c r="D13" s="52" t="inlineStr">
+      <c r="D13" s="58" t="inlineStr">
         <is>
           <t>Sí. Guarda una copia del archivo por empresa o por periodo (Archivo &gt; Guardar como) y deja el original en blanco como plantilla maestra.</t>
         </is>
@@ -2997,12 +3213,12 @@
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="n"/>
-      <c r="C16" s="53" t="inlineStr">
+      <c r="C16" s="59" t="inlineStr">
         <is>
           <t>COTIZACIÓN</t>
         </is>
       </c>
-      <c r="D16" s="54" t="inlineStr">
+      <c r="D16" s="60" t="inlineStr">
         <is>
           <t>Oferta formal de precio por parte de un proveedor.</t>
         </is>
@@ -3012,12 +3228,12 @@
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="4" t="n"/>
-      <c r="C17" s="53" t="inlineStr">
+      <c r="C17" s="59" t="inlineStr">
         <is>
           <t>REQUISICIÓN</t>
         </is>
       </c>
-      <c r="D17" s="54" t="inlineStr">
+      <c r="D17" s="60" t="inlineStr">
         <is>
           <t>Solicitud interna de compra.</t>
         </is>
@@ -3027,12 +3243,12 @@
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="4" t="n"/>
-      <c r="C18" s="53" t="inlineStr">
+      <c r="C18" s="59" t="inlineStr">
         <is>
           <t>CONDICIONES COMERCIALES</t>
         </is>
       </c>
-      <c r="D18" s="54" t="inlineStr">
+      <c r="D18" s="60" t="inlineStr">
         <is>
           <t>Crédito, garantía y entrega.</t>
         </is>
@@ -3059,12 +3275,12 @@
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="4" t="n"/>
-      <c r="B21" s="55" t="inlineStr">
+      <c r="B21" s="61" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C21" s="56" t="inlineStr">
+      <c r="C21" s="62" t="inlineStr">
         <is>
           <t>Requisición autorizada</t>
         </is>
@@ -3074,12 +3290,12 @@
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="4" t="n"/>
-      <c r="B22" s="55" t="inlineStr">
+      <c r="B22" s="61" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C22" s="56" t="inlineStr">
+      <c r="C22" s="62" t="inlineStr">
         <is>
           <t>Cotizaciones recibidas con la misma especificación</t>
         </is>
@@ -3089,12 +3305,12 @@
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="n"/>
-      <c r="B23" s="55" t="inlineStr">
+      <c r="B23" s="61" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C23" s="56" t="inlineStr">
+      <c r="C23" s="62" t="inlineStr">
         <is>
           <t>Cuadro llenado y firmado</t>
         </is>
@@ -3104,12 +3320,12 @@
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="4" t="n"/>
-      <c r="B24" s="55" t="inlineStr">
+      <c r="B24" s="61" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C24" s="56" t="inlineStr">
+      <c r="C24" s="62" t="inlineStr">
         <is>
           <t>Proveedor seleccionado notificado</t>
         </is>
